--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -10,13 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fora da janela" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ausentes da Crítica" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aparece sem defeito nele" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$3:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$3:$C$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$L$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Aparece sem defeito nele'!$A$3:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$N$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -449,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 137 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão em três é a que a base sustenta, não a que o rótulo diz.</t>
+          <t>Os 137 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>
@@ -508,174 +506,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ausentes — não aparecem em papel nenhum</t>
+          <t>Ausentes — nunca tiveram defeito aberto neles</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>não há ocorrência para mostrar</t>
+          <t>não há distância para medir</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aparecem, mas nunca com defeito nele</t>
+          <t xml:space="preserve">  · não aparecem na Crítica em papel nenhum</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>52</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · aparecem só como interrompidos ou manobrados</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>23</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>interrompido ou manobrado — sem distância</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ordem dele, lidos um a um</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FAIXAS DE TEMPO — só os que têm registro em outra data</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  até 24 horas</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>21% dos 62</t>
-        </is>
-      </c>
+          <t>FAIXAS DE TEMPO — só os que têm registro em outra data</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1 a 7 dias</t>
+          <t xml:space="preserve">  até 24 horas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>29% dos 62</t>
+          <t>21% dos 62</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7 a 30 dias</t>
+          <t xml:space="preserve">  1 a 7 dias</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23% dos 62</t>
+          <t>29% dos 62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1 a 3 meses</t>
+          <t xml:space="preserve">  7 a 30 dias</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18% dos 62</t>
+          <t>23% dos 62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">  1 a 3 meses</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>18% dos 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  mais de 3 meses</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>6</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>10% dos 62</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a mais perto da janela</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>horas</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mediana</t>
+          <t xml:space="preserve">  a mais perto da janela</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dias</t>
+          <t>horas</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  mediana</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  a mais longe</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>182</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>dias</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C19"/>
+  <autoFilter ref="A3:C20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -5086,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5094,19 +5103,21 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="66" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="66" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>52 solicitações cujo código não aparece na Crítica em papel nenhum — nem com defeito, nem interrompido, nem manobrado — nos sete meses do acervo. As colunas de ocorrência e de atendimento vêm vazias de propósito: não existe registro, e mostrar “a ocorrência mais próxima” seria inventar vínculo. A única ligação é o teste do vizinho, que aponta ocorrência em OUTRO ativo do mesmo alimentador — hipótese, não prova.</t>
+          <t>75 solicitações em que a Crítica nunca registrou defeito aberto no próprio transformador, em data nenhuma dos sete meses. A coluna “Por que é ausente” separa os dois jeitos: o código não aparecer em papel nenhum, ou aparecer só como interrompido e manobrado — que é o que acontece com quem fica sem energia por defeito de outro equipamento. As colunas de ocorrência e de atendimento vêm escritas como “— nenhuma”: não existe registro, e mostrar “a ocorrência mais próxima” seria inventar vínculo.</t>
         </is>
       </c>
     </row>
@@ -5138,35 +5149,45 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Por que é ausente</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Papéis na Crítica</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Ocorrência no dossiê</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Atendimento do TMAE</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Como está vinculado</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Teste do vizinho</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Texto da SS</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Obra</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Trafos no material</t>
         </is>
@@ -5200,31 +5221,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Mesmo alimentador: ocorrência 20264104966246 no ativo 8849950257 (12/02 07:32 a 12/02 13:19) — número operativo provavelmente trocado</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>SEGUE SS PARA SUBSTITUIR TRAFO QEUIMADO NA RDR DE PINDORAMAOBS: NOTA CRIADA PARA SUBST. A SS 800/2025 QUE FOI ABERTA NO TRAFO ERRADO</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5256,31 +5287,41 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Mesmo alimentador: ocorrência 20264104966246 no ativo 8849950257 (12/02 07:32 a 12/02 13:19) — número operativo provavelmente trocado</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>SEGUE SS PARA SUBSTITUIR TRAFO QUEIMADO OBS: NOTA CRIADA PARA SUBST. SS 814/2025 ABERTA NO TRAFO ERRADO</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5312,35 +5353,45 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Mesma localidade: ocorrência 20264155609284 no ativo 8802619001 (02/03 21:10) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>segue nota trafo queimado de 45kVA paraio bom</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5372,1792 +5423,2060 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Mesmo alimentador: ocorrência 20264163700248 no ativo 7900366256 (05/03 18:43 a 05/03 20:55) — número operativo provavelmente trocado</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TR 5710079256 queimado</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00003/2026</t>
+          <t>DG-RD-PO 00333/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5700121151</t>
+          <t>5700494044</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SANTA TEREZA DO TOCANTINS</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>AL01032044</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-02 15:28</t>
+          <t>2026-04-14 17:47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264062660526 no ativo 5704441122 (02/01 10:01 a 02/01 18:24) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 30 kvar e 03 para raio queimado da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso bom cliente penalizado 01 equipe que atendeu 151op01 cel, 63992629128/984188058 favor agilizar o atendimento devido cliente informar que está com 03 dias sem energia</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ss para trocar trafo 5700494044 e para raio queimado POTENCIA: 15KVA 7.9KVACESSO CAMINHONETE, CARRO FICA A 30 METROS DO LOCAL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00303/2026</t>
+          <t>DOLP-RD-PA 00003/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5722285006</t>
+          <t>5700121151</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOCANTINIA</t>
+          <t>SANTA TEREZA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LD03059122</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-28 08:04</t>
+          <t>2026-01-02 15:28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264150076340 no ativo 5710991006 (27/02 18:13 a 28/02 15:40) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>trafo 5722285006 vazaMENTO DE Óleo acesso livre potencia 30 kva tensão 34,5 para-raio queimado obs: leva porta fusivel para fecha o trafo</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+          <t>Mesmo alimentador: ocorrência 20264062660526 no ativo 5704441122 (02/01 10:01 a 02/01 18:24) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>segue ss de 01 trafo de 30 kvar e 03 para raio queimado da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso bom cliente penalizado 01 equipe que atendeu 151op01 cel, 63992629128/984188058 favor agilizar o atendimento devido cliente informar que está com 03 dias sem energia</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00552/2026</t>
+          <t>DOLP-RD-PA 00125/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5365343122</t>
+          <t>5700307083</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>APARECIDA DO RIO NEGRO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL04099059</t>
+          <t>LD03059122</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-12 17:38</t>
+          <t>2026-01-25 20:09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>interrompido em 1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264388434563 no ativo 5700133122 (12/05 13:55 a 13/05 11:40) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 25 kvar e 01 para raio queimado da rede de 13.800kv e para raio queimado para ser subistituido pela equipe de manutencão  acesso livre equipe que atendeu 059op14 cel,  63992432595/985159679 chave de referencia, 5365343122</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Segue SS para atendimento com equipe de manutenção , substituir trafo 5700307083 com VAZ. DE OLEO na RDR de aparecida do rio negro , acesso para CAMIONETE , para-raio queimado , tensão 34,5, potencia 5 kva</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00621/2026</t>
+          <t>DOLP-RD-PA 00303/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5711684122</t>
+          <t>5722285006</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>TOCANTINIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD03059122</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-01 12:34</t>
+          <t>2026-02-28 08:04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264467284665 no ativo 5303924122 (01/06 11:33 a 01/06 14:08) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TRAFO 5711684122 QUEIMADOPOTÊNCIA: 15 KVATENSÃO: 19,9 KVACESSO: LIVRE</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+          <t>Mesmo alimentador: ocorrência 20264150076340 no ativo 5710991006 (27/02 18:13 a 28/02 15:40) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>trafo 5722285006 vazaMENTO DE Óleo acesso livre potencia 30 kva tensão 34,5 para-raio queimado obs: leva porta fusivel para fecha o trafo</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00024/2026</t>
+          <t>DOLP-RD-PA 00382/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5700559233</t>
+          <t>5763161196</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VILA LUZIMANGUES</t>
+          <t>LAGOA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LD02050008</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-06 18:36</t>
+          <t>2026-03-24 14:14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264066841216 no ativo 4020087149 (05/01 15:01 a 07/01 22:27) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>segue SS ´para tratativa com equipe de manutençao subtituir trafo 5700559233 na rdr de abreulandia</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264197357546 no ativo 0310038151 (24/03 09:04 a 24/03 14:29) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SEGUE SS DE TRAFO 5763161196 QUEIMADO NA RDR DE LAGOA DO TOCANTINS. PARA AS DEVIDAS TRATATIVAS COM EQUIPE DE MANUTENÇÃOOBS: LEVAR JOGO DE CHAVE FUSIVEL PARA INSTALAR NA MESMA ESTRUTURA DE TRAFO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00044/2026</t>
+          <t>DOLP-RD-PA 00437/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5710028046</t>
+          <t>5704106122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL01056046</t>
+          <t>AL05097122</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-11 10:38</t>
+          <t>2026-04-09 12:30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264071671751 no ativo 0360132046 (11/01 02:32) — conferir número de série do equipamento retirado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TR 571002804610KVA13800PARA RAIO DANIFICADO ACESSO PARA CAMINHONETE (1)UC PENALIZADA EM CAMPO 046OP01 VILSON</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>segue nota de trafo queimado, trafo 5704106122, trafo de 45kva, tensao 13800 / 380 V, para raio danificado, acesso livre</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00057/2026</t>
+          <t>DOLP-RD-PA 00552/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5710441149</t>
+          <t>5365343122</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CASEARA</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LD03414149</t>
+          <t>AL04099059</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-01-12 17:10</t>
+          <t>2026-05-12 17:38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Mesma localidade: ocorrência 20264079559001 no ativo 5700414149 (12/01 09:45) — conferir número de série do equipamento retirado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>TR 571044114930KVAT 34500PARA RAIO DANIFICADO ACESSO PARA CAMINHAO (1) PENALIZADA WELVIS SUP. DIVINOPOLIS</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+          <t>Mesmo alimentador: ocorrência 20264388434563 no ativo 5700133122 (12/05 13:55 a 13/05 11:40) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>segue ss de 01 trafo de 25 kvar e 01 para raio queimado da rede de 13.800kv e para raio queimado para ser subistituido pela equipe de manutencão  acesso livre equipe que atendeu 059op14 cel,  63992432595/985159679 chave de referencia, 5365343122</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00259/2026</t>
+          <t>DOLP-RD-PA 00588/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5700191054</t>
+          <t>5761649196</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PUGMIL</t>
+          <t>LAGOA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LD01056046</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-20 13:46</t>
+          <t>2026-05-24 00:11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264132739596 no ativo 0300191054 (20/02 08:43 a 22/02 07:41) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>substituir poste ID 47042587 10/300 estrutura do TR 5700191054 15KVA 19,9KV ACESSO BOM fotos anexadas na OS 20264131749370</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00358/2026</t>
+          <t>DOLP-RD-PA 00621/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5700460055</t>
+          <t>5711684122</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARAGUACEMA</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LD01434149</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-17 18:55</t>
+          <t>2026-06-01 12:34</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Mesma localidade: ocorrência 20264182680114 no ativo 5700411055 (17/03 09:48) — conferir número de série do equipamento retirado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>TR 5763273055 15KVAPARA RAIO DANIFICADO ACESSO LIVRE PARA CAMINHONETE 055OP01 ESTEVE NO LOCAL TRAFO NAO AXISTE NO SISTEMA (ERRO CADASTRO) FICA PROX AO TR 5700460055MAIS INFORMAÇOES ENTRA EM CONTATO COM EQUIPE 055OP01</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264467284665 no ativo 5303924122 (01/06 11:33 a 01/06 14:08) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>TRAFO 5711684122 QUEIMADOPOTÊNCIA: 15 KVATENSÃO: 19,9 KVACESSO: LIVRE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00361/2026</t>
+          <t>ENC-RD-PS 00024/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5701007008</t>
+          <t>5700559233</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MIRANORTE</t>
+          <t>VILA LUZIMANGUES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AL02050008</t>
+          <t>LD02050008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-19 10:47</t>
+          <t>2026-01-06 18:36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264186839193 no ativo 5700636008 (18/03 16:35 a 19/03 18:54) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OS:20264186004963Segue SS de TR queimado UC 9222677 e 3635120 TR não cadastrado 15KVA/7.9KV e para-raios queimados.Acesso livre.Localização: https://www.google.com/maps/search/?api=1&amp;query=-9.534713,-48.600728 SS aberta no TR 5701007008 porém o que está queimado é outro.FAZENDA BOA SORTE63984910222 </t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264066841216 no ativo 4020087149 (05/01 15:01 a 07/01 22:27) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>segue SS ´para tratativa com equipe de manutençao subtituir trafo 5700559233 na rdr de abreulandia</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00438/2026</t>
+          <t>ENC-RD-PS 00044/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5701060070</t>
+          <t>5710028046</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RIO SONO</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LD01059122</t>
+          <t>AL01056046</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-07 15:20</t>
+          <t>2026-01-11 10:38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264262669137 no ativo 5752349092 (06/04 11:25 a 07/04 16:39) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Segue SS de trafo 5701096007 queimado para devidas trativas com equipe de manutenção.Potencia 15 kvatensão 34.5kv para raio bomacesso livre OBS: trafo com erro de cadastro, o mesmo esta cadastrado na rededa 13.8 porem em campo esta ligado na rede da 34.5 kv. trafo fica localizado ao lado do trafo 57</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>Mesma localidade: ocorrência 20264071671751 no ativo 0360132046 (11/01 02:32) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>TR 571002804610KVA13800PARA RAIO DANIFICADO ACESSO PARA CAMINHONETE (1)UC PENALIZADA EM CAMPO 046OP01 VILSON</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00546/2026</t>
+          <t>ENC-RD-PS 00054/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5701119075</t>
+          <t>5701203084</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DOIS IRMAOS DO TOCANTINS</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LD02050008</t>
+          <t>LD03414149</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-01 16:44</t>
+          <t>2026-01-12 13:21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264467783590 no ativo 3310079075 (01/06 13:00 a 01/06 21:28) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5701119075 15KVA 34,5KV ACESSO BOM E PARA-RAIOS 075OP02</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antes susbtituir trafo 5701203084 queimado na rdr de divinopoles</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00594/2026</t>
+          <t>ENC-RD-PS 00057/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5700417110</t>
+          <t>5710441149</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SANTA RITA DO TOCANTINS</t>
+          <t>CASEARA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LD06047073</t>
+          <t>LD03414149</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-21 13:30</t>
+          <t>2026-01-12 17:10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>TRAFO 5700417110 DE 5 KVA NA REDE 19.9 KV QUEIMADO ACESSO BOM TROCAR E O POSTE DO TRAFO ID: 47152336 POIS O MESMO NÃO SUPORTA O TRAFO DE 15 E FINO E O POSTE ANTES DA CHAVE TRAFO 0300417110 NO ID: 68938875 PARA FAZER O SERVIÇO TEM ABRIR CHAVE LAMINA PROXIMO AO TRAFO 5700399073.</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>POSTE DANIFICADO</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
+          <t>Mesma localidade: ocorrência 20264079559001 no ativo 5700414149 (12/01 09:45) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>TR 571044114930KVAT 34500PARA RAIO DANIFICADO ACESSO PARA CAMINHAO (1) PENALIZADA WELVIS SUP. DIVINOPOLIS</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00437/2026</t>
+          <t>ENC-RD-PS 00177/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5700145002</t>
+          <t>5701299084</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TOCANTINOPOLIS</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AL01084002</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-22 08:06</t>
+          <t>2026-02-02 14:50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264312501533 no ativo 5700323145 (21/04 13:28 a 22/04 10:13) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Segue SS de TR 5700145002 15KVA/7.9KV avariado com a bucha primária trincada e vazamento de óleo nas buchas secundárias.Acesso livre.UC 218774DISTRITO SANITARIO ESPECIAL INDIGENA TOCANTINSJoison 63 98404-8858</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+          <t>Mesmo alimentador: ocorrência 20264113078601 no ativo 5701350084 (31/01 11:04 a 02/02 15:30) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5701299084</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00489/2026</t>
+          <t>ENC-RD-PS 00259/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5701350103</t>
+          <t>5700191054</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAO MIGUEL DO TOCANTINS</t>
+          <t>PUGMIL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LD01014045</t>
+          <t>LD01056046</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-08 12:16</t>
+          <t>2026-02-20 13:46</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Mesma localidade: ocorrência 20264270977071 no ativo 0322983103 (08/05 09:30) — conferir número de série do equipamento retirado</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Segue SS de transformador 5701350103 Queimado Potencia 10 KVA Tensão: 19.9 KVAcesso livre Fazenda Jangada. Assentamento Camarão II</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+          <t>Mesmo alimentador: ocorrência 20264132739596 no ativo 0300191054 (20/02 08:43 a 22/02 07:41) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>substituir poste ID 47042587 10/300 estrutura do TR 5700191054 15KVA 19,9KV ACESSO BOM fotos anexadas na OS 20264131749370</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DANO(S) CAUSADO POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00508/2026</t>
+          <t>ENC-RD-PS 00358/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5701508039</t>
+          <t>5700460055</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARAGUATINS</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LD02109039</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-15 13:32</t>
+          <t>2026-03-17 18:55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264399998658 no ativo 3301459039 (15/05 07:53 a 15/05 14:08) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>trafo queimado 5701508039 - 15KVA - 34,5KV - para raio queimado - acesso caminhonete. IND CHACARA BOA ESPERANCA - cliente: JUNHO ALVES DE SOUSA - 63992753298REF PROX AO PEQUENO E AO VALDINAR RDR ARAGUATINS</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>Mesma localidade: ocorrência 20264182680114 no ativo 5700411055 (17/03 09:48) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>TR 5763273055 15KVAPARA RAIO DANIFICADO ACESSO LIVRE PARA CAMINHONETE 055OP01 ESTEVE NO LOCAL TRAFO NAO AXISTE NO SISTEMA (ERRO CADASTRO) FICA PROX AO TR 5700460055MAIS INFORMAÇOES ENTRA EM CONTATO COM EQUIPE 055OP01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00001/2026</t>
+          <t>ENC-RD-PS 00361/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5703016016</t>
+          <t>5701007008</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>MIRANORTE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>AL02050008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-01-02 10:17</t>
+          <t>2026-03-19 10:47</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264062439510 no ativo 5700285080 (02/01 09:06 a 02/01 18:30) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>SUBSTITUIR o Trafo 5703016016Lançar vão de rede de 100 metros , cabo AA / 4Instalar chave trafo ELO 0,5HAcesso livrePotencia de 15 kVA</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264186839193 no ativo 5700636008 (18/03 16:35 a 19/03 18:54) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OS:20264186004963Segue SS de TR queimado UC 9222677 e 3635120 TR não cadastrado 15KVA/7.9KV e para-raios queimados.Acesso livre.Localização: https://www.google.com/maps/search/?api=1&amp;query=-9.534713,-48.600728 SS aberta no TR 5701007008 porém o que está queimado é outro.FAZENDA BOA SORTE63984910222 </t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00024/2026</t>
+          <t>ENC-RD-PS 00438/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5756806060</t>
+          <t>5701060070</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>RIO SONO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AL02054060</t>
+          <t>LD01059122</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-01-06 20:40</t>
+          <t>2026-04-07 15:20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>TRAFO 5756806060 75KVA 13.8KV COM VAZAMENTO DE OLEO, ATENDE UMA ESCOLA DR. HELIO DE SOU BUENO NA RDU DE NOVA OLINDA</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+          <t>Mesmo alimentador: ocorrência 20264262669137 no ativo 5752349092 (06/04 11:25 a 07/04 16:39) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Segue SS de trafo 5701096007 queimado para devidas trativas com equipe de manutenção.Potencia 15 kvatensão 34.5kv para raio bomacesso livre OBS: trafo com erro de cadastro, o mesmo esta cadastrado na rededa 13.8 porem em campo esta ligado na rede da 34.5 kv. trafo fica localizado ao lado do trafo 57</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00081/2026</t>
+          <t>ENC-RD-PS 00546/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5704370057</t>
+          <t>5701119075</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>DOIS IRMAOS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD02050008</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-01-16 08:57</t>
+          <t>2026-06-01 16:44</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264085921158 no ativo 5710036159 (13/01 08:36 a 18/01 10:26) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Trafo 5704370057 15 kva queimadoTensão: 19.9Acesso: Livre Endereço: IND FAZENDA NOVO HORIZONTE, 0 - NOVO HORIZONTE 500M DA  PISTA</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+          <t>Mesmo alimentador: ocorrência 20264467783590 no ativo 3310079075 (01/06 13:00 a 01/06 21:28) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5701119075 15KVA 34,5KV ACESSO BOM E PARA-RAIOS 075OP02</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00118/2026</t>
+          <t>ENC-RD-PS 00594/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5700746004</t>
+          <t>5700417110</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>SANTA RITA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD06047073</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-01-19 21:44</t>
+          <t>2026-06-21 13:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264088345566 no ativo 0301967022 (19/01 18:29 a 20/01 12:00) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Trafo 5700746004 queimado 15kvaTensão: 19.9Acesso somente para caminhoneteEquipe: 004op08</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>TRAFO 5700417110 DE 5 KVA NA REDE 19.9 KV QUEIMADO ACESSO BOM TROCAR E O POSTE DO TRAFO ID: 47152336 POIS O MESMO NÃO SUPORTA O TRAFO DE 15 E FINO E O POSTE ANTES DA CHAVE TRAFO 0300417110 NO ID: 68938875 PARA FAZER O SERVIÇO TEM ABRIR CHAVE LAMINA PROXIMO AO TRAFO 5700399073.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>POSTE DANIFICADO</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00207/2026</t>
+          <t>ETO-RD-AG 00164/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5366985025</t>
+          <t>5700032103</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>SAO MIGUEL DO TOCANTINS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LD02010153</t>
+          <t>LD01076103</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-02 13:43</t>
+          <t>2026-02-07 19:18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>interrompido em 3 · manobrado em 3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264115220045 no ativo 5700489136 (02/02 07:43 a 02/02 16:09) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Boa noite,Favor enviar manutenção para subsitutir trafo 5366985025</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>trafo queimado</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00243/2026</t>
+          <t>ETO-RD-AG 00249/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5701262019</t>
+          <t>5700696045</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LD01105019</t>
+          <t>LD03014045</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-04 18:47</t>
+          <t>2026-03-03 12:18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264116079654 no ativo 5754932019 (03/02 12:19 a 05/02 16:24) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Trafo 5701262019 avariado 15kvaTensão: 19.9Acesso livre</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>POSTE DANIFICADO</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>TROCA DE TRAFO 5700696045 QUEIMADO DE 30KVA DA 34.5 PARA RAIOS QUEIMADO. ACESSO BOMTROCAR JOGO DE CHAVESUBSTITUIR OS GLV'SLEVAR ROLDANA DA BT.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00415/2026</t>
+          <t>ETO-RD-AG 00437/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5700402060</t>
+          <t>5700145002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>TOCANTINOPOLIS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AL01054060</t>
+          <t>AL01084002</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-03 20:22</t>
+          <t>2026-04-22 08:06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264158896692 no ativo 64745653 (03/03 16:36 a 03/03 21:00) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>TR-5700402060 vazando oleo para raios bompotência 10kvatensão 13,8kvacesso livreequipe 060op0102 tel-63992173964</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264312501533 no ativo 5700323145 (21/04 13:28 a 22/04 10:13) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Segue SS de TR 5700145002 15KVA/7.9KV avariado com a bucha primária trincada e vazamento de óleo nas buchas secundárias.Acesso livre.UC 218774DISTRITO SANITARIO ESPECIAL INDIGENA TOCANTINSJoison 63 98404-8858</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00437/2026</t>
+          <t>ETO-RD-AG 00489/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5701771022</t>
+          <t>5701350103</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>SAO MIGUEL DO TOCANTINS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD01014045</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-07 13:00</t>
+          <t>2026-05-08 12:16</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264165948657 no ativo 5702442004 (07/03 10:14 a 07/03 14:35) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Trafo 5701771022 queimado 15kvaTensão: 34.5Acesso; somente para caminhonteEquipe: 004op27Endereço: Chacara Bela Vista</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>Mesma localidade: ocorrência 20264270977071 no ativo 0322983103 (08/05 09:30) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Segue SS de transformador 5701350103 Queimado Potencia 10 KVA Tensão: 19.9 KVAcesso livre Fazenda Jangada. Assentamento Camarão II</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00440/2026</t>
+          <t>ETO-RD-AG 00508/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5701182022</t>
+          <t>5701508039</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>ARAGUATINS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LD04105019</t>
+          <t>LD02109039</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-08 11:28</t>
+          <t>2026-05-15 13:32</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Mesma localidade: ocorrência 20264166045879 no ativo 5701358022 (07/03 18:28) — conferir número de série do equipamento retirado</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Bom dia Segue SSSenhores envia equipe na RDR de Babaçulândia para trocar poste e Trafo Trafo: 5701182022Poste: 10/200ID: 55662476Acesso:  Para caminhão e caminhoneteEndereço: Chácara Cantinho Pov. FarturãoOBS: Trocar poste e Trafo.</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>POSTE DANIFICADO</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+          <t>Mesmo alimentador: ocorrência 20264399998658 no ativo 3301459039 (15/05 07:53 a 15/05 14:08) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>trafo queimado 5701508039 - 15KVA - 34,5KV - para raio queimado - acesso caminhonete. IND CHACARA BOA ESPERANCA - cliente: JUNHO ALVES DE SOUSA - 63992753298REF PROX AO PEQUENO E AO VALDINAR RDR ARAGUATINS</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>ETO-RD-AG 00545/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5301889004</t>
+          <t>5700724045</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AL02096004</t>
+          <t>LD03014045</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-12 19:30</t>
+          <t>2026-05-22 15:23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264174095227 no ativo 244R094 (12/03 17:06 a 12/03 20:11) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Trafo 570188904 queimado 15kvaAcesso: Somente caminhonetePara-raio; Queimado Equipe: 004op26</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>segue trafo 5700724045 com vazamento de oleo pot. 25 kva tensão 19,9kvpara-raio ruimacesso bom</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00557/2026</t>
+          <t>ETO-RD-AR 00001/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5710138077</t>
+          <t>5703016016</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AL01042078</t>
+          <t>LD02010004</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-26 08:51</t>
+          <t>2026-01-02 10:17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264201423278 no ativo 5720177077 (26/03 07:28 a 26/03 10:54) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>TR-5710138077 o mesmo não esta entregando a tensão adequadapara queimadopotência 10kvatensão 13,8kvacesso livreequipe 265op0 tel-63992212789</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
+          <t>Mesmo alimentador: ocorrência 20264062439510 no ativo 5700285080 (02/01 09:06 a 02/01 18:30) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SUBSTITUIR o Trafo 5703016016Lançar vão de rede de 100 metros , cabo AA / 4Instalar chave trafo ELO 0,5HAcesso livrePotencia de 15 kVA</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00576/2026</t>
+          <t>ETO-RD-AR 00024/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5100722193</t>
+          <t>5756806060</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PS01112193</t>
+          <t>AL02054060</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-30 20:05</t>
+          <t>2026-01-06 20:40</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264225986217 no ativo 5700800193 (30/03 18:03) — conferir número de série do equipamento retirado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Segue trafo 5100722193 queimado, trafo atende RL 7900722193 SUPRIMENTO CEMAR, ACESSO LIVRETENSÃO 19,9KV POT. 15KVAPARA-RAIO BOMRELIGADOR ESTA SEM COMUNICAÇÃO DEVIDO PROBLEMA DO TRAFO NECESSITA URGENCIA</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>TRAFO 5756806060 75KVA 13.8KV COM VAZAMENTO DE OLEO, ATENDE UMA ESCOLA DR. HELIO DE SOU BUENO NA RDU DE NOVA OLINDA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00582/2026</t>
+          <t>ETO-RD-AR 00081/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5710015080</t>
+          <t>5704370057</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-31 20:03</t>
+          <t>2026-01-16 08:57</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264243488362 no ativo 5700499080 (31/03 16:14 a 01/04 09:25) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Trafo: 5710015080 QueimadoPotência: 15 KVARede: 34.5Pararaio: 34.5Acesso: só pra veículo traçadoSubstituir o mesmo pois está com a bucha primária quebrado por descarga atmosférica</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264085921158 no ativo 5710036159 (13/01 08:36 a 18/01 10:26) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Trafo 5704370057 15 kva queimadoTensão: 19.9Acesso: Livre Endereço: IND FAZENDA NOVO HORIZONTE, 0 - NOVO HORIZONTE 500M DA  PISTA</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00658/2026</t>
+          <t>ETO-RD-AR 00118/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5761134022</t>
+          <t>5700746004</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7167,2120 +7486,2899 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-04-10 10:56</t>
+          <t>2026-01-19 21:44</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264273385891 no ativo 5701014022 (09/04 22:50 a 10/04 11:13) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>trafo 5761134022 75kva 34.5kv queimado</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264088345566 no ativo 0301967022 (19/01 18:29 a 20/01 12:00) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Trafo 5700746004 queimado 15kvaTensão: 19.9Acesso somente para caminhoneteEquipe: 004op08</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00690/2026</t>
+          <t>ETO-RD-AR 00207/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5766930077</t>
+          <t>5366985025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-04-16 12:36</t>
+          <t>2026-02-02 13:43</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264292326563 no ativo 5701389077 (16/04 10:30 a 16/04 15:07) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Boa tarde,Favor enviar manutenção para verificar trafo com vazamento de oleo no comutador de TAPTensão: 34,5Potencia: 15 kvaPara raio bomACESSO LIVREChacara Deus e Fiel</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
+          <t>Mesmo alimentador: ocorrência 20264115220045 no ativo 5700489136 (02/02 07:43 a 02/02 16:09) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Boa noite,Favor enviar manutenção para subsitutir trafo 5366985025</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00700/2026</t>
+          <t>ETO-RD-AR 00243/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5710170025</t>
+          <t>5701262019</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>FILADELFIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LD02010153</t>
+          <t>LD01105019</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-04-17 14:38</t>
+          <t>2026-02-04 18:47</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264294400667 no ativo 5710135136 (17/04 08:41 a 17/04 15:29) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>trafo 5710170025 queimado acesso bom para caminhonete 25kvaequipe 025op01</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
+          <t>Mesmo alimentador: ocorrência 20264116079654 no ativo 5754932019 (03/02 12:19 a 05/02 16:24) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Trafo 5701262019 avariado 15kvaTensão: 19.9Acesso livre</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>POSTE DANIFICADO</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00763/2026</t>
+          <t>ETO-RD-AR 00315/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5710235080</t>
+          <t>5702058004</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>AL04096004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-04-29 08:53</t>
+          <t>2026-02-15 23:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>interrompido em 2 · manobrado em 2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264340843377 no ativo 5700331053 (27/04 08:49 a 29/04 17:00) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NOTA ABERTA PARA CORREÇÃO DA SS 751/2026 POIS O TRAFO QUE ESTAVA QUEIMADO E O 5710235080</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>trafo faltanto fase interno secundaria 5702058004 e com vazamento de oleopot 30kvatensao 34,5kvacesso caminhonetefazenda sao paulo GRANJA</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00773/2026</t>
+          <t>ETO-RD-AR 00415/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5700290030</t>
+          <t>5700402060</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>AL01054060</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-04-29 18:02</t>
+          <t>2026-03-03 20:22</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264326949336 no ativo 3300990016 (25/04 11:41 a 30/04 12:24) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>TRAFO QUEIMADO 5700920030POTENCIA: 5KVATENSÃO: 34,5KVACESSO BOM.PARA-RAIO QUEIMADO.FAZ. MORENA 1</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
+          <t>Mesmo alimentador: ocorrência 20264158896692 no ativo 64745653 (03/03 16:36 a 03/03 21:00) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>TR-5700402060 vazando oleo para raios bompotência 10kvatensão 13,8kvacesso livreequipe 060op0102 tel-63992173964</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00775/2026</t>
+          <t>ETO-RD-AR 00434/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5700702019</t>
+          <t>5710028040</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>ARAGOMINAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LD04105019</t>
+          <t>AL01006040</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-30 11:15</t>
+          <t>2026-03-06 22:17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>nada — sobe para campo</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Trafo 5700702019 15kvaAcesso: Livre Equipe:019op02Contato da equipe : 99242-6260</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Trafo 5710028040 Queimado Potencia:15 KVATensão: 13,8 KVPara raio: Queimado Acesso: CamionetaEquipe: 040op36 (63)992870450</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00818/2026</t>
+          <t>ETO-RD-AR 00437/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5710240030</t>
+          <t>5701771022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-08 19:27</t>
+          <t>2026-03-07 13:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264375607668 no ativo 3310142053 (08/05 16:16 a 08/05 20:30) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Trafo 5710240030 Vazamento de oleoPotencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 030op01 (63)98468-3634</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
+          <t>Mesmo alimentador: ocorrência 20264165948657 no ativo 5702442004 (07/03 10:14 a 07/03 14:35) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Trafo 5701771022 queimado 15kvaTensão: 34.5Acesso; somente para caminhonteEquipe: 004op27Endereço: Chacara Bela Vista</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00052/2026</t>
+          <t>ETO-RD-AR 00440/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5741943048</t>
+          <t>5701182022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LD02038009</t>
+          <t>LD04105019</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-09 18:59</t>
+          <t>2026-03-08 11:28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264070942400 no ativo 5700193048 (09/01 15:23 a 10/01 15:16) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>trafo queimado 5710088048, porem em campo esta o trafo 5741943048112.5 kVAacesso livre pararaio queimadoequipe 009op01- 63999201531</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
+          <t>Mesma localidade: ocorrência 20264166045879 no ativo 5701358022 (07/03 18:28) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bom dia Segue SSSenhores envia equipe na RDR de Babaçulândia para trocar poste e Trafo Trafo: 5701182022Poste: 10/200ID: 55662476Acesso:  Para caminhão e caminhoneteEndereço: Chácara Cantinho Pov. FarturãoOBS: Trocar poste e Trafo.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>POSTE DANIFICADO</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00095/2026</t>
+          <t>ETO-RD-AR 00468/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5700396048</t>
+          <t>5301889004</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LD02038009</t>
+          <t>AL02096004</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-16 16:33</t>
+          <t>2026-03-12 19:30</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Trafo: 5700396048 Avariado Potencia: 15 KVATensão: 34,5kPara raio: queimado Acesso: Camioneta   Equipe: 009op02 (63)99983-3829Obs. trafo esta com tensão baixa em uma das buchas.</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264174095227 no ativo 244R094 (12/03 17:06 a 12/03 20:11) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Trafo 570188904 queimado 15kvaAcesso: Somente caminhonetePara-raio; Queimado Equipe: 004op26</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00140/2026</t>
+          <t>ETO-RD-AR 00504/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5700922009</t>
+          <t>5752570159</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GUARAI</t>
+          <t>MURICILANDIA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LD04038009</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-28 20:04</t>
+          <t>2026-03-17 20:04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264105160221 no ativo 5700923009 (28/01 19:38 a 29/01 13:05) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>TR-5700922009 Queimadopara raios queiamado potência 10kvatensão 34,5kvacesso livreequipe 009op01 tel-63984566867</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264182949787 no ativo 5701421060 (17/03 09:54 a 17/03 22:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5752570159 30kva 34.5kv e para raioacesso livre</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00174/2026</t>
+          <t>ETO-RD-AR 00555/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5747088104</t>
+          <t>5702259004</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOM JESUS DO TOCANTINS</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-03 13:24</t>
+          <t>2026-03-25 19:39</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264113090887 no ativo 5728426129 (31/01 10:20 a 04/02 06:20) — número operativo provavelmente trocado</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>trafo queimado 5747088104 - 15KVA - 34,5KV - Acesso caminhonete - para raio queimadofazenda conquista - cliente Jose Reis Amario da Silva tel. 9.92521087 rdr Bom Jesus do Tocantins</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>trafo queimado 5702259004 queimado 15 kv 19,9 kva para raio Bom acesso bom.fazenda Santa Tereza - UC 3165559-0 cliente: Persio de Freitas Vilela. RDR Arapoema</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00189/2026</t>
+          <t>ETO-RD-AR 00557/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5700424154</t>
+          <t>5710138077</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JUARINA</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>AL01042078</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-04 18:05</t>
+          <t>2026-03-26 08:51</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264117059087 no ativo 5700315153 (03/02 18:07 a 04/02 21:41) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>TR-5700424154 Queimadopara raios queiamdo potência 10kvatensão 34,5kvacesso livreequipe 154op01 tel-63992674347</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
+          <t>Mesmo alimentador: ocorrência 20264201423278 no ativo 5720177077 (26/03 07:28 a 26/03 10:54) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>TR-5710138077 o mesmo não esta entregando a tensão adequadapara queimadopotência 10kvatensão 13,8kvacesso livreequipe 265op0 tel-63992212789</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00233/2026</t>
+          <t>ETO-RD-AR 00576/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5700569227</t>
+          <t>5100722193</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RECURSOLANDIA</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>PS01112193</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-15 13:28</t>
+          <t>2026-03-30 20:05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264128670467 no ativo 0310003104 (15/02 09:04 a 16/02 11:33) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>TRAFO 5745261227 SAI COM RDU DO TRAFO 5700013227 E FICA  A FRENTE DO TRAFO 5700569227 QUEIMADO PARA RAIO TAMBÉM DE 15 KVA NA NA REDE 19,9 KV ACESSO BOM PARA CAMIONETE FOI FEITO TESTE AVAZIO COSTATADO QUEIMADO COM VAZAMENTO DE ÓLEO</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>Mesma localidade: ocorrência 20264225986217 no ativo 5700800193 (30/03 18:03) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Segue trafo 5100722193 queimado, trafo atende RL 7900722193 SUPRIMENTO CEMAR, ACESSO LIVRETENSÃO 19,9KV POT. 15KVAPARA-RAIO BOMRELIGADOR ESTA SEM COMUNICAÇÃO DEVIDO PROBLEMA DO TRAFO NECESSITA URGENCIA</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00259/2026</t>
+          <t>ETO-RD-AR 00582/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5710023113</t>
+          <t>5710015080</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COUTO MAGALHAES</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>LD02010004</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-21 13:09</t>
+          <t>2026-03-31 20:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264133424374 no ativo 5700054034 (20/02 17:32 a 21/02 14:01) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>trafo queimado 5710023113 - 15KVA - 34,5KV acesso caminhonete para raio queimado necessario refazer aterramento IND ASSENTAMEN P.A. UNIAO, 0 - CHA JANDAIAuc 562509263991206181 -RDR COUTO MAGALHAES</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264243488362 no ativo 5700499080 (31/03 16:14 a 01/04 09:25) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Trafo: 5710015080 QueimadoPotência: 15 KVARede: 34.5Pararaio: 34.5Acesso: só pra veículo traçadoSubstituir o mesmo pois está com a bucha primária quebrado por descarga atmosférica</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00292/2026</t>
+          <t>ETO-RD-AR 00658/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5710447023</t>
+          <t>5761134022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL01020023</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-26 19:07</t>
+          <t>2026-04-10 10:56</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Mesma localidade: ocorrência 20264144238723 no ativo 5700284023 (26/02 10:01) — conferir número de série do equipamento retirado</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Boa noite,Favor enviar manutenção para substituir trafo queimado 5710447023</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>Mesmo alimentador: ocorrência 20264273385891 no ativo 5701014022 (09/04 22:50 a 10/04 11:13) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>trafo 5761134022 75kva 34.5kv queimado</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00400/2026</t>
+          <t>ETO-RD-AR 00690/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5700214066</t>
+          <t>5766930077</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TUPIRATINS</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LD03038009</t>
+          <t>LD03105019</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-03 10:19</t>
+          <t>2026-04-16 12:36</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>acionar equipe de manutencao para troca do poste e transformador no RDR de [0066] TUPIRATINStrafo 5700214066poste 10-300 id.: 49935819  estrutura u3-Tequipe 034op03</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
+          <t>Mesmo alimentador: ocorrência 20264292326563 no ativo 5701389077 (16/04 10:30 a 16/04 15:07) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Boa tarde,Favor enviar manutenção para verificar trafo com vazamento de oleo no comutador de TAPTensão: 34,5Potencia: 15 kvaPara raio bomACESSO LIVREChacara Deus e Fiel</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00598/2026</t>
+          <t>ETO-RD-AR 00700/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5730596155</t>
+          <t>5710170025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-04 17:41</t>
+          <t>2026-04-17 14:38</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264477692067 no ativo 4000514155 (04/06 16:31 a 04/06 18:04) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Boa tarde,Favor enviar manutenção para substituir trafo 5730596155 o mesmo está com muito vazamento de oléo. Se possivel colocar trafo de maior potencia.</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
+          <t>Mesmo alimentador: ocorrência 20264294400667 no ativo 5710135136 (17/04 08:41 a 17/04 15:29) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>trafo 5710170025 queimado acesso bom para caminhonete 25kvaequipe 025op01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00073/2026</t>
+          <t>ETO-RD-AR 00742/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5701108076</t>
+          <t>5710274030</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CARIRI DO TOCANTINS</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LD02040003</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-14 16:27</t>
+          <t>2026-04-25 18:08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264082974240 no ativo 5715146076 (14/01 10:38 a 15/01 21:01) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>transformador e para  raio queimado</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
+          <t>Mesmo alimentador: ocorrência 20264326949336 no ativo 3300990016 (25/04 11:41 a 30/04 12:24) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5710274030 transformador,esta com vazamento de óleo. Mas sem interrupção de Energia. 5 kVA. da 19.9 Local de livre acesso para caminhonete. Para raios bom</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>ETO-RD-AR 00763/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5710235080</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DARCINOPOLIS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LD02010004</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-04-29 08:53</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264340843377 no ativo 5700331053 (27/04 08:49 a 29/04 17:00) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NOTA ABERTA PARA CORREÇÃO DA SS 751/2026 POIS O TRAFO QUE ESTAVA QUEIMADO E O 5710235080</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00773/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5700290030</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PIRAQUE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LD01095030</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:02</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264326949336 no ativo 3300990016 (25/04 11:41 a 30/04 12:24) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>TRAFO QUEIMADO 5700920030POTENCIA: 5KVATENSÃO: 34,5KVACESSO BOM.PARA-RAIO QUEIMADO.FAZ. MORENA 1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00775/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5700702019</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FILADELFIA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LD04105019</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Trafo 5700702019 15kvaAcesso: Livre Equipe:019op02Contato da equipe : 99242-6260</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00818/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5710240030</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>XAMBIOA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LD01095030</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-08 19:27</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264375607668 no ativo 3310142053 (08/05 16:16 a 08/05 20:30) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Trafo 5710240030 Vazamento de oleoPotencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 030op01 (63)98468-3634</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00872/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5710241016</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>WANDERLANDIA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LD01095030</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-17 17:55</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264403490105 no ativo 5710176016 (16/05 18:23 a 17/05 18:20) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Trafo 5710241016 Queimado Potencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 004op26 (63)99214-9597</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ETO-RD-AR 00987/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5700001058</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SANTA FE DO ARAGUAIA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LD04010004</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:57</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>interrompido em 4 · manobrado em 4</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>TRAFO 5700001058 75KVA 34.5KV COM VAZAMENTO DE OLEO OCASIONANDO INCENDIO NA BUCHA SECUNDARIARUA JOSE LINO DA SILVA, 0 - QD07 LT 04 PROX CARTORIO DE IMOVEIS RDU DE SANTA FÉ.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00248/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5700456038</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TAGUATINGA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LD01414027</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:14</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264302437570 no ativo 5710057038 (19/04 08:48 a 19/04 15:14) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>trafo e para raio queimado 5700456038 15kva 19.9kv faz.oriente rdr de taguatinga equipe 038op01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00052/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5741943048</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FORTALEZA DO TABOCAO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LD02038009</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-01-09 18:59</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264070942400 no ativo 5700193048 (09/01 15:23 a 10/01 15:16) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>trafo queimado 5710088048, porem em campo esta o trafo 5741943048112.5 kVAacesso livre pararaio queimadoequipe 009op01- 63999201531</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00095/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5700396048</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FORTALEZA DO TABOCAO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LD02038009</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-01-16 16:33</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Trafo: 5700396048 Avariado Potencia: 15 KVATensão: 34,5kPara raio: queimado Acesso: Camioneta   Equipe: 009op02 (63)99983-3829Obs. trafo esta com tensão baixa em uma das buchas.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00140/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5700922009</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GUARAI</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LD04038009</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-01-28 20:04</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264105160221 no ativo 5700923009 (28/01 19:38 a 29/01 13:05) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>TR-5700922009 Queimadopara raios queiamado potência 10kvatensão 34,5kvacesso livreequipe 009op01 tel-63984566867</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00174/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5747088104</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BOM JESUS DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LD01065015</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-02-03 13:24</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264113090887 no ativo 5728426129 (31/01 10:20 a 04/02 06:20) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>trafo queimado 5747088104 - 15KVA - 34,5KV - Acesso caminhonete - para raio queimadofazenda conquista - cliente Jose Reis Amario da Silva tel. 9.92521087 rdr Bom Jesus do Tocantins</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00189/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5700424154</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>JUARINA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LD01010153</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-02-04 18:05</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264117059087 no ativo 5700315153 (03/02 18:07 a 04/02 21:41) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>TR-5700424154 Queimadopara raios queiamdo potência 10kvatensão 34,5kvacesso livreequipe 154op01 tel-63992674347</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00233/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5700569227</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RECURSOLANDIA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LD01065015</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-02-15 13:28</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264128670467 no ativo 0310003104 (15/02 09:04 a 16/02 11:33) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>TRAFO 5745261227 SAI COM RDU DO TRAFO 5700013227 E FICA  A FRENTE DO TRAFO 5700569227 QUEIMADO PARA RAIO TAMBÉM DE 15 KVA NA NA REDE 19,9 KV ACESSO BOM PARA CAMIONETE FOI FEITO TESTE AVAZIO COSTATADO QUEIMADO COM VAZAMENTO DE ÓLEO</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00259/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5710023113</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>COUTO MAGALHAES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LD02020023</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-02-21 13:09</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264133424374 no ativo 5700054034 (20/02 17:32 a 21/02 14:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>trafo queimado 5710023113 - 15KVA - 34,5KV acesso caminhonete para raio queimado necessario refazer aterramento IND ASSENTAMEN P.A. UNIAO, 0 - CHA JANDAIAuc 562509263991206181 -RDR COUTO MAGALHAES</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00292/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5710447023</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COLINAS DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AL01020023</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:07</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mesma localidade: ocorrência 20264144238723 no ativo 5700284023 (26/02 10:01) — conferir número de série do equipamento retirado</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Boa noite,Favor enviar manutenção para substituir trafo queimado 5710447023</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00295/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5710173023</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>COLINAS DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AL05020023</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-02-27 15:07</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Boa tarde,Favor enviar manutenção para subsitutir trafo com bucha secundaria com defeito 5710173023Obs: Necessario substituir cruzeta deterioradaEstrutura: N3</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00400/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5700214066</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TUPIRATINS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LD03038009</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:19</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>acionar equipe de manutencao para troca do poste e transformador no RDR de [0066] TUPIRATINStrafo 5700214066poste 10-300 id.: 49935819  estrutura u3-Tequipe 034op03</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00598/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5730596155</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PALMEIRANTE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LD02020023</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:41</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264477692067 no ativo 4000514155 (04/06 16:31 a 04/06 18:04) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Boa tarde,Favor enviar manutenção para substituir trafo 5730596155 o mesmo está com muito vazamento de oléo. Se possivel colocar trafo de maior potencia.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00632/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5700782153</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BERNARDO SAYAO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LD01010153</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-06-19 15:57</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264537119402 no ativo 5700249025 (19/06 08:13 a 20/06 09:51) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>TRANSFORMADOR DE 10KVA NA 34,5KV, QUEIMADO, ACESSO CAMINHONETE.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00066/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5710535094</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PEIXE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LD01066094</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-01-13 20:52</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264080676346 no ativo 46810578 (13/01 09:23 a 14/01 19:34) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>transformador e para raio queimado</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00073/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5701108076</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CARIRI DO TOCANTINS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LD02040003</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:27</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264082974240 no ativo 5715146076 (14/01 10:38 a 15/01 21:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>transformador e para  raio queimado</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00218/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5710863003</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GURUPI</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LD02001037</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-02-16 19:10</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264129144150 no ativo 5700423041 (16/02 14:05 a 17/02 09:20) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>TRAFO 5710863003 QUEIMADO EM CAMPO DE 15 KVA ACESSO PARA CAMIONETE PARA RAIO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00377/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5731386073</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LAGOA DA CONFUSAO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LD06047073</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-03-23 18:27</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 2</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>TRAFO 5731386073 QUEIMADO EM CAMPO DE 15 KVA ACESSO APENAS DE BARCO REGIAO ALAGADAPARA RAIO QUEIMADO   .</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00440/2026</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>5700284148</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>SAO VALERIO</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>LD01066094</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>2026-04-07 18:19</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>não aparece em papel nenhum</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Mesmo alimentador: ocorrência 20264265758791 no ativo 5700693148 (07/04 11:01 a 08/04 11:30) — número operativo provavelmente trocado</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE SAO VALERIO, TRAFO DE 15KVA NA REDE DE 19.9KV, TRAFO E PARARAIO QUEIMADO, ACESSO LIVRE PARA CAMINHONETE.</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="N78" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L55"/>
+  <autoFilter ref="A3:N78"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>23 solicitações em que o código APARECE na Crítica, mas nunca como o elemento com defeito: só como interrompido ou manobrado. Para estas não existe distância até a janela, e por isso elas não entram na distribuição de tempo da primeira aba. Hoje o site as classifica junto das de fora da janela — é o assunto que ficou em aberto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Transformador</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Localidade</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Abertura da SS</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Papéis na Crítica</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Texto da SS</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Obra</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Trafos no material</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00333/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5700494044</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-14 17:47</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ss para trocar trafo 5700494044 e para raio queimado POTENCIA: 15KVA 7.9KVACESSO CAMINHONETE, CARRO FICA A 30 METROS DO LOCAL</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00125/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5700307083</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>APARECIDA DO RIO NEGRO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-25 20:09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>interrompido em 1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Segue SS para atendimento com equipe de manutenção , substituir trafo 5700307083 com VAZ. DE OLEO na RDR de aparecida do rio negro , acesso para CAMIONETE , para-raio queimado , tensão 34,5, potencia 5 kva</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00382/2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5763161196</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LAGOA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-24 14:14</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SEGUE SS DE TRAFO 5763161196 QUEIMADO NA RDR DE LAGOA DO TOCANTINS. PARA AS DEVIDAS TRATATIVAS COM EQUIPE DE MANUTENÇÃOOBS: LEVAR JOGO DE CHAVE FUSIVEL PARA INSTALAR NA MESMA ESTRUTURA DE TRAFO</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00437/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5704106122</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PALMAS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-09 12:30</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>segue nota de trafo queimado, trafo 5704106122, trafo de 45kva, tensao 13800 / 380 V, para raio danificado, acesso livre</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00588/2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5761649196</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LAGOA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-24 00:11</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00054/2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>5701203084</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-01-12 13:21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antes susbtituir trafo 5701203084 queimado na rdr de divinopoles</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00177/2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5701299084</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-02-02 14:50</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5701299084</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ETO-RD-AG 00164/2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5700032103</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SAO MIGUEL DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-02-07 19:18</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>interrompido em 3 · manobrado em 3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>trafo queimado</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ETO-RD-AG 00249/2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5700696045</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AUGUSTINOPOLIS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-03 12:18</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>TROCA DE TRAFO 5700696045 QUEIMADO DE 30KVA DA 34.5 PARA RAIOS QUEIMADO. ACESSO BOMTROCAR JOGO DE CHAVESUBSTITUIR OS GLV'SLEVAR ROLDANA DA BT.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ETO-RD-AG 00545/2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5700724045</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AUGUSTINOPOLIS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-22 15:23</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>segue trafo 5700724045 com vazamento de oleo pot. 25 kva tensão 19,9kvpara-raio ruimacesso bom</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00315/2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5702058004</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ARAGUAINA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-15 23:00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>interrompido em 2 · manobrado em 2</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>trafo faltanto fase interno secundaria 5702058004 e com vazamento de oleopot 30kvatensao 34,5kvacesso caminhonetefazenda sao paulo GRANJA</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00434/2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5710028040</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ARAGOMINAS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:17</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Trafo 5710028040 Queimado Potencia:15 KVATensão: 13,8 KVPara raio: Queimado Acesso: CamionetaEquipe: 040op36 (63)992870450</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00504/2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5752570159</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MURICILANDIA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-17 20:04</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5752570159 30kva 34.5kv e para raioacesso livre</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00555/2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5702259004</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ARAGUAINA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-25 19:39</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>trafo queimado 5702259004 queimado 15 kv 19,9 kva para raio Bom acesso bom.fazenda Santa Tereza - UC 3165559-0 cliente: Persio de Freitas Vilela. RDR Arapoema</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00742/2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5710274030</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>XAMBIOA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-25 18:08</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>5710274030 transformador,esta com vazamento de óleo. Mas sem interrupção de Energia. 5 kVA. da 19.9 Local de livre acesso para caminhonete. Para raios bom</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO AVARIADO</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00872/2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5710241016</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>WANDERLANDIA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-05-17 17:55</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Trafo 5710241016 Queimado Potencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 004op26 (63)99214-9597</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00987/2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5700001058</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SANTA FE DO ARAGUAIA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-06-16 18:57</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>interrompido em 4 · manobrado em 4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>TRAFO 5700001058 75KVA 34.5KV COM VAZAMENTO DE OLEO OCASIONANDO INCENDIO NA BUCHA SECUNDARIARUA JOSE LINO DA SILVA, 0 - QD07 LT 04 PROX CARTORIO DE IMOVEIS RDU DE SANTA FÉ.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ETO-RD-DP 00248/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5700456038</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TAGUATINGA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-19 12:14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>trafo e para raio queimado 5700456038 15kva 19.9kv faz.oriente rdr de taguatinga equipe 038op01</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ETO-RD-GR 00295/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5710173023</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>COLINAS DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-02-27 15:07</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Boa tarde,Favor enviar manutenção para subsitutir trafo com bucha secundaria com defeito 5710173023Obs: Necessario substituir cruzeta deterioradaEstrutura: N3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ETO-RD-GR 00632/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5700782153</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BERNARDO SAYAO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-06-19 15:57</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>TRANSFORMADOR DE 10KVA NA 34,5KV, QUEIMADO, ACESSO CAMINHONETE.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00066/2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5710535094</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PEIXE</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-01-13 20:52</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>transformador e para raio queimado</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00218/2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>5710863003</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GURUPI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-16 19:10</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>manobrado em 1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>TRAFO 5710863003 QUEIMADO EM CAMPO DE 15 KVA ACESSO PARA CAMIONETE PARA RAIO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00377/2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5731386073</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LAGOA DA CONFUSAO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-23 18:27</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>interrompido em 1 · manobrado em 2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>TRAFO 5731386073 QUEIMADO EM CAMPO DE 15 KVA ACESSO APENAS DE BARCO REGIAO ALAGADAPARA RAIO QUEIMADO   .</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:H26"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$3:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$N$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 137 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
+          <t>Os 118 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21% dos 62</t>
+          <t>19% dos 43</t>
         </is>
       </c>
     </row>
@@ -580,11 +580,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29% dos 62</t>
+          <t>28% dos 43</t>
         </is>
       </c>
     </row>
@@ -595,11 +595,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23% dos 62</t>
+          <t>28% dos 43</t>
         </is>
       </c>
     </row>
@@ -610,11 +610,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18% dos 62</t>
+          <t>16% dos 43</t>
         </is>
       </c>
     </row>
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10% dos 62</t>
+          <t>9% dos 43</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>62 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
+          <t>43 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
         </is>
       </c>
     </row>
@@ -805,27 +805,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00604/2026</t>
+          <t>DOLP-RD-PA 00458/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5700006193</t>
+          <t>5700873122</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PS01112193</t>
+          <t>AL04060122</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-02 08:40</t>
+          <t>2026-04-15 15:02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
         <v>0.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20264250485039</t>
+          <t>20264288661473</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-02 10:22</t>
+          <t>2026-04-15 17:25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>trafo 5700006193 e para raio queimado na RDU de campos lindo com 118uc penalizada equipe 193op01 acesso lvre</t>
+          <t>Transformador 5700873122 com vazamento de oleo grande proporção, potencia 112.5kva tensão 13.8 acesso livre a caminhao para raio bom, cabo aa/2,QP 120.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -874,27 +874,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00458/2026</t>
+          <t>ETO-RD-AG 00501/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5700873122</t>
+          <t>5700105132</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>SAMPAIO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AL04060122</t>
+          <t>LD02014045</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-15 15:02</t>
+          <t>2026-05-13 07:19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="H5" t="n">
         <v>0.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20264288661473</t>
+          <t>20264391468820</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-15 17:25</t>
+          <t>2026-05-13 10:15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -924,11 +924,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Transformador 5700873122 com vazamento de oleo grande proporção, potencia 112.5kva tensão 13.8 acesso livre a caminhao para raio bom, cabo aa/2,QP 120.</t>
+          <t>Enviar equipe de manutenção para substituir trafo com vazamento de oleo na bucha secundária fase A - TRAFO 5700105132 - 5KVA-19.9KV</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -943,27 +943,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00501/2026</t>
+          <t>DOLP-RD-PA 00521/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5700105132</t>
+          <t>5703327122</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAMPAIO</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LD02014045</t>
+          <t>AL05059122</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-13 07:19</t>
+          <t>2026-05-02 18:51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -972,19 +972,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
         <v>0.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20264391468820</t>
+          <t>20264354214073</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-13 10:15</t>
+          <t>2026-05-02 22:20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Enviar equipe de manutenção para substituir trafo com vazamento de oleo na bucha secundária fase A - TRAFO 5700105132 - 5KVA-19.9KV</t>
+          <t>SEGUE SS DE TRAFO 5703327122 COM VAZAMENTO DE OLEO, NA RDU DE PALMASPOTENCIA 45KVAQUADRA 206 SULOBS: SE POSSIVEL LEVAR UM TRAFO DE MAIOR POTENCIA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1012,27 +1012,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00353/2026</t>
+          <t>ETO-RD-AG 00493/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5700349001</t>
+          <t>5700265045</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AL02057189</t>
+          <t>LD03014045</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-25 11:37</t>
+          <t>2026-05-09 16:40</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>0.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20264326584228</t>
+          <t>20264378533481</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-25 15:00</t>
+          <t>2026-05-09 20:10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>trafo 5700349001 queimado de 15 kva acesso livre oara raio queimado tensao 13.8 kv local e pusado levar trafo de 25 kva se possivel e levar cahve fusivel completa da 13.8 kv rdr de porto nacional</t>
+          <t>Constatado trafo 5700265045 de 10kVA na 19,9kV com vazamento de óleo. Melhores informações falar com Denismar 63 99972-2277</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1081,27 +1081,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00521/2026</t>
+          <t>ETO-RD-AG 00327/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5703327122</t>
+          <t>5700119039</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>ARAGUATINS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AL05059122</t>
+          <t>AL01109039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-02 18:51</t>
+          <t>2026-03-24 16:47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20264354214073</t>
+          <t>20264197663442</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-02 22:20</t>
+          <t>2026-03-24 21:44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO 5703327122 COM VAZAMENTO DE OLEO, NA RDU DE PALMASPOTENCIA 45KVAQUADRA 206 SULOBS: SE POSSIVEL LEVAR UM TRAFO DE MAIOR POTENCIA</t>
+          <t>TRAFO 5700119039 COM VAZAMENTO DE OLEO DE 75KVA DA 13.8. ACESSO LIVRE. TRAFO ENERGIZADO.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1150,27 +1150,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00493/2026</t>
+          <t>DG-RD-PO 00209/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5700265045</t>
+          <t>5700237001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>PORTO NACIONAL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LD03014045</t>
+          <t>AL06072001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-09 16:40</t>
+          <t>2026-02-20 20:29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1179,24 +1179,24 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>14.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20264378533481</t>
+          <t>20264133314401</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-09 20:10</t>
+          <t>2026-02-21 11:18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Constatado trafo 5700265045 de 10kVA na 19,9kV com vazamento de óleo. Melhores informações falar com Denismar 63 99972-2277</t>
+          <t>SEGUE SS DE TRAFO 5700237001 COM BUCHA PRIMARIA QUEBRADA PARA DEVIDAS TRATATIVAS COM EQUIPE DE MANUTENÇÃO.POTENCIA: 75 KVATENÇÃO: 13,8 KV ACESSO LIVRE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1219,27 +1219,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00327/2026</t>
+          <t>ETO-RD-GR 00324/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5700119039</t>
+          <t>5700006034</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARAGUATINS</t>
+          <t>PRESIDENTE KENNEDY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL01109039</t>
+          <t>AL01073034</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-24 16:47</t>
+          <t>2026-03-10 08:34</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>15.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20264197663442</t>
+          <t>20264171353629</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-24 21:44</t>
+          <t>2026-03-10 23:48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>TRAFO 5700119039 COM VAZAMENTO DE OLEO DE 75KVA DA 13.8. ACESSO LIVRE. TRAFO ENERGIZADO.</t>
+          <t>trafo 5700006034 com vazamento de oleo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1288,27 +1288,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00405/2026</t>
+          <t>ETO-RD-GR 00167/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5700001112</t>
+          <t>5710328113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COLMEIA</t>
+          <t>COUTO MAGALHAES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LD03022033</t>
+          <t>LD03020023</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-06 16:56</t>
+          <t>2026-02-02 10:49</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1317,37 +1317,37 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>23.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20264259245529</t>
+          <t>20264116127370</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-06 22:19</t>
+          <t>2026-02-03 10:36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>acionar equipe de manutencao para troca de trafo avariado na RDU de Goainir dos campos e chave danificada fase Atrafo 5700001112Equipe 033po01</t>
+          <t>trafo vazando oleo, levar porta fusivel</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1357,66 +1357,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00436/2026</t>
+          <t>ETO-RD-GR 00387/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5701067004</t>
+          <t>5700018155</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD02105019</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-06 22:28</t>
+          <t>2026-03-27 09:49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11.5</v>
+        <v>24.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20264165000179</t>
+          <t>20264201727493</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-07 10:00</t>
+          <t>2026-03-25 14:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CHAVE FUSIVEL/RELIGADORA</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trafo 5701067004 Queimado Potencia: 15 KVATensão: 34,5 KVPara raio: Queimado Acesso: Camioneta Equipe: 004op33 (63)99200-2367</t>
+          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1426,48 +1426,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00209/2026</t>
+          <t>ENC-RD-PS 00487/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5700237001</t>
+          <t>5700002253</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>CHAPADA DE AREIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL06072001</t>
+          <t>LD03062013</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-20 20:29</t>
+          <t>2026-04-29 13:51</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14.8</v>
+        <v>28.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20264133314401</t>
+          <t>20264348037836</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-02-21 11:18</t>
+          <t>2026-04-30 18:04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1476,16 +1476,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO 5700237001 COM BUCHA PRIMARIA QUEBRADA PARA DEVIDAS TRATATIVAS COM EQUIPE DE MANUTENÇÃO.POTENCIA: 75 KVATENÇÃO: 13,8 KV ACESSO LIVRE</t>
+          <t>TR 5700002253MUITO VAZAMENTO DE OLEO 150 KVA34500PARA RAIO BOM ACESSO LIVRE013OP014 HEMINIO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1495,48 +1495,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00324/2026</t>
+          <t>ETO-RD-AR 00204/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5700006034</t>
+          <t>5723118030</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PRESIDENTE KENNEDY</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AL01073034</t>
+          <t>LD02095030</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-10 08:34</t>
+          <t>2026-02-02 07:07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>15.2</v>
+        <v>35.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20264171353629</t>
+          <t>20264112025210</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-10 23:48</t>
+          <t>2026-01-30 08:49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>trafo 5700006034 com vazamento de oleo</t>
+          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1564,61 +1564,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00058/2026</t>
+          <t>ETO-RD-GR 00466/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5700144029</t>
+          <t>5710404111</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PALMEIROPOLIS</t>
+          <t>PEQUIZEIRO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AL01061029</t>
+          <t>LD03020023</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-01-12 14:04</t>
+          <t>2026-04-22 07:20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19</v>
+        <v>38.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20264078542689</t>
+          <t>20264307303463</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-01-13 09:03</t>
+          <t>2026-04-20 09:11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>segue ss para troca de trafo queimado</t>
+          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,48 +1633,48 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00167/2026</t>
+          <t>DOLP-RD-PA 00124/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5710328113</t>
+          <t>5711933122</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COUTO MAGALHAES</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LD03020023</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-02 10:49</t>
+          <t>2026-01-25 12:35</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23.8</v>
+        <v>60.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20264116127370</t>
+          <t>20264092758229</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-02-03 10:36</t>
+          <t>2026-01-22 11:47</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1683,11 +1683,11 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>trafo vazando oleo, levar porta fusivel</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1702,27 +1702,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00387/2026</t>
+          <t>DOLP-RD-PA 00177/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5700018155</t>
+          <t>5755307026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LD02105019</t>
+          <t>LD06002091</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-27 09:49</t>
+          <t>2026-02-03 08:31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1731,24 +1731,24 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>24.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20264201727493</t>
+          <t>20264113211342</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-03-25 14:00</t>
+          <t>2026-01-30 11:15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CHAVE FUSIVEL/RELIGADORA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
+          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1771,27 +1771,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00185/2026</t>
+          <t>DG-RD-PO 00160/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5700472026</t>
+          <t>5753553037</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>BREJINHO DE NAZARE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD02001037</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-13 12:23</t>
+          <t>2026-02-04 09:56</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>26.8</v>
+        <v>68</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20264128083816</t>
+          <t>20264113024457</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-02-14 15:09</t>
+          <t>2026-01-30 10:22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Segue SS para substituiçaõ de trafo queimado</t>
+          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1840,27 +1840,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00487/2026</t>
+          <t>DOLP-RD-PA 00338/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5700002253</t>
+          <t>5704202122</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHAPADA DE AREIA</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LD03062013</t>
+          <t>AL01099059</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-29 13:51</t>
+          <t>2026-03-10 16:17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1869,37 +1869,37 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>28.2</v>
+        <v>72.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20264348037836</t>
+          <t>20264165847819</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-30 18:04</t>
+          <t>2026-03-07 08:49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CONDUTOR DE BT</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TR 5700002253MUITO VAZAMENTO DE OLEO 150 KVA34500PARA RAIO BOM ACESSO LIVRE013OP014 HEMINIO</t>
+          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1909,27 +1909,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00101/2026</t>
+          <t>ETO-RD-AR 00583/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5744418082</t>
+          <t>5700799193</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LIZARDA</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LD02065015</t>
+          <t>LD03105019</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-01-20 13:26</t>
+          <t>2026-03-31 20:47</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1938,32 +1938,32 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>29.9</v>
+        <v>72.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20264090305646</t>
+          <t>20264208594801</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-01-21 19:21</t>
+          <t>2026-03-27 17:30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Transformador avariado o mesmo nao distribui, 5744418082, potencia 30kva, tensão 34.5, para raio queimado e acesso livre a camionete.</t>
+          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1972,33 +1972,33 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00204/2026</t>
+          <t>ETO-RD-AR 00774/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5723118030</t>
+          <t>5743290004</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LD02095030</t>
+          <t>AL01040004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-02 07:07</t>
+          <t>2026-04-30 11:05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2007,24 +2007,24 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35.8</v>
+        <v>118.9</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20264112025210</t>
+          <t>20264326606216</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-01-30 08:49</t>
+          <t>2026-04-25 11:38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
+          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2047,27 +2047,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00466/2026</t>
+          <t>ETO-RD-GR 00278/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5710404111</t>
+          <t>5700216064</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PEQUIZEIRO</t>
+          <t>BRASILANDIA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LD03020023</t>
+          <t>LD02020023</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-04-22 07:20</t>
+          <t>2026-02-23 20:17</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>38.6</v>
+        <v>142.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20264307303463</t>
+          <t>20264152703110</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-20 09:11</t>
+          <t>2026-03-01 18:21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
+          <t>trafo 5700216064 com bucha danificada 15KVA 34,5KV para raio bom acesso livre. chacara firmeza - RDR BrasilandiaThiago Pires Moral - UC 3283572-0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2116,27 +2116,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00124/2026</t>
+          <t>ETO-RD-GR 00373/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5711933122</t>
+          <t>5700725023</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>COLINAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>AL02020023</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-01-25 12:35</t>
+          <t>2026-03-23 18:37</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2145,19 +2145,19 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>60.7</v>
+        <v>165.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20264092758229</t>
+          <t>20264213656808</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-01-22 11:47</t>
+          <t>2026-03-30 16:08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
+          <t>por favor desloca equipe da manutenção pesada no trafo 5700725023 com vazamento oleo 112,5 kva na 13,8kv acesso bom urgente RDU</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2185,61 +2185,61 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00177/2026</t>
+          <t>ETO-RD-AR 00268/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5755307026</t>
+          <t>5700382016</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LD06002091</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-03 08:31</t>
+          <t>2026-02-08 11:20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>64.40000000000001</v>
+        <v>234.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20264113211342</t>
+          <t>20264106536555</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-01-30 11:15</t>
+          <t>2026-01-27 19:13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
+          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,61 +2254,61 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00160/2026</t>
+          <t>ETO-RD-AR 00551/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5753553037</t>
+          <t>5700322060</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BREJINHO DE NAZARE</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LD02001037</t>
+          <t>AL01054060</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-04 09:56</t>
+          <t>2026-03-24 17:26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>68</v>
+        <v>242.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20264113024457</t>
+          <t>20264177286410</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-01-30 10:22</t>
+          <t>2026-03-13 17:12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2323,61 +2323,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00338/2026</t>
+          <t>ETO-RD-DP 00214/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5704202122</t>
+          <t>5700230116</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>PINDORAMA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AL01099059</t>
+          <t>LD03046026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-10 16:17</t>
+          <t>2026-03-23 13:59</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>72.2</v>
+        <v>243.7</v>
       </c>
       <c r="H26" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20264175511481</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-03-12 15:36</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TRANSFORMADOR</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>3</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20264165847819</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-03-07 08:49</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>CONDUTOR DE BT</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
+          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2392,48 +2392,48 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00224/2026</t>
+          <t>ETO-RD-AR 00034/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5700849077</t>
+          <t>5700867040</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>ARAGOMINAS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-02-04 09:32</t>
+          <t>2026-01-08 10:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>72.59999999999999</v>
+        <v>289.9</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>12.1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20264120786868</t>
+          <t>20254051242939</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-02-07 10:07</t>
+          <t>2025-12-26 18:28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>BOA TARDE,FAVOR ENVIAR MANUTENÇÃO PARA SUBSTITUIR TRAFO QUEIMADO 5700849077</t>
+          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2461,53 +2461,53 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00583/2026</t>
+          <t>ETO-RD-GR 00238/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5700799193</t>
+          <t>5710058153</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>BERNARDO SAYAO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>LD01010153</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-31 20:47</t>
+          <t>2026-02-16 12:35</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>72.8</v>
+        <v>399.9</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>16.7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20264208594801</t>
+          <t>20264112068933</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-27 17:30</t>
+          <t>2026-01-30 17:52</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
+          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2530,61 +2530,61 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00315/2026</t>
+          <t>ETO-RD-AR 00484/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5702271001</t>
+          <t>5702075022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AL02057189</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-09 01:06</t>
+          <t>2026-03-15 13:37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>81.09999999999999</v>
+        <v>506.3</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4</v>
+        <v>21.1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20264279754412</t>
+          <t>20264133539002</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-04-12 10:11</t>
+          <t>2026-02-22 07:31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO</t>
+          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2599,53 +2599,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00774/2026</t>
+          <t>ETO-RD-AR 00188/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5743290004</t>
+          <t>5739688157</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AL01040004</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-30 11:05</t>
+          <t>2026-01-30 11:44</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>118.9</v>
+        <v>595.4</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>24.8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20264326606216</t>
+          <t>20264066876544</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-04-25 11:38</t>
+          <t>2026-01-05 14:21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
+          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2668,48 +2668,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00278/2026</t>
+          <t>ETO-RD-AR 00463/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5700216064</t>
+          <t>5701543077</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BRASILANDIA DO TOCANTINS</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>AL01042078</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-23 20:17</t>
+          <t>2026-03-11 21:10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>142.1</v>
+        <v>607.3</v>
       </c>
       <c r="H31" t="n">
-        <v>5.9</v>
+        <v>25.3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20264152703110</t>
+          <t>20264127861374</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-01 18:21</t>
+          <t>2026-02-13 18:53</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2718,11 +2718,11 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>trafo 5700216064 com bucha danificada 15KVA 34,5KV para raio bom acesso livre. chacara firmeza - RDR BrasilandiaThiago Pires Moral - UC 3283572-0</t>
+          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2737,48 +2737,48 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00284/2026</t>
+          <t>ENC-RD-PS 00008/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5731254026</t>
+          <t>5700188046</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LD03046026</t>
+          <t>LD01056046</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-21 15:15</t>
+          <t>2026-01-03 18:05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>147.2</v>
+        <v>609.4</v>
       </c>
       <c r="H32" t="n">
-        <v>6.1</v>
+        <v>25.4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20264208138102</t>
+          <t>20254011736926</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-27 18:29</t>
+          <t>2025-12-08 14:48</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2787,11 +2787,11 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>trafo avariado</t>
+          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2800,59 +2800,59 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00408/2026</t>
+          <t>ETO-RD-GR 00023/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5710230159</t>
+          <t>5700005195</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MURICILANDIA</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD01065015</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-02 17:20</t>
+          <t>2026-01-05 12:18</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>162.8</v>
+        <v>621.8</v>
       </c>
       <c r="H33" t="n">
-        <v>6.8</v>
+        <v>25.9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20264168752391</t>
+          <t>20254016315055</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-03-09 12:07</t>
+          <t>2025-12-10 13:52</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>TRAFO 5710230159 DE 15 KVA NA DE 19.9 QUEIMADO PARA RAIO TAMBÉM ACESSO BOM FEITO TESTE AVAZIO CONSTATADO QUEIMADO COM VAZAMENTO DE ÓLEO</t>
+          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -2875,48 +2875,48 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00373/2026</t>
+          <t>DOLP-RD-PA 00122/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5700725023</t>
+          <t>5710169006</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>TOCANTINIA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AL02020023</t>
+          <t>LD05050008</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-23 18:37</t>
+          <t>2026-01-25 10:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>165.5</v>
+        <v>674.2</v>
       </c>
       <c r="H34" t="n">
-        <v>6.9</v>
+        <v>28.1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20264213656808</t>
+          <t>20254052989150</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-03-30 16:08</t>
+          <t>2025-12-27 12:21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>por favor desloca equipe da manutenção pesada no trafo 5700725023 com vazamento oleo 112,5 kva na 13,8kv acesso bom urgente RDU</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2944,27 +2944,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00268/2026</t>
+          <t>ETO-RD-AG 00117/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5700382016</t>
+          <t>5700011032</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>LD01008032</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-02-08 11:20</t>
+          <t>2026-01-30 18:32</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2973,24 +2973,24 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>234.3</v>
+        <v>690.6</v>
       </c>
       <c r="H35" t="n">
-        <v>9.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20264106536555</t>
+          <t>20264152604502</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-01-27 19:13</t>
+          <t>2026-02-28 13:07</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
+          <t>TRafo 5710001103 de 15KVA na 19.9KV com vazamento de oleo lLocal: Povoado Buriti na RDR de São MiguelAcesso livre</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>POSTE DANIFICADO</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3013,66 +3013,66 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00317/2026</t>
+          <t>DG-RD-PO 00064/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5700011086</t>
+          <t>5711513001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARIANOPOLIS DO TOCANTINS</t>
+          <t>PORTO NACIONAL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LD05062013</t>
+          <t>AL03062013</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-08 12:41</t>
+          <t>2026-01-16 03:49</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>235.4</v>
+        <v>733</v>
       </c>
       <c r="H36" t="n">
-        <v>9.800000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20264139615540</t>
+          <t>20254025928206</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-03-18 08:08</t>
+          <t>2025-12-15 14:53</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>DISTRIBUICAO PROGRAMADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>segue ss para tratativa com equipe de manutençao o quanto antes substituir trafo 5700011086 queimado na rdu de marianopoles leva 80 metros de cabo mutiplex cabo 35leva 1 porta fusivel da 34,5</t>
+          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3082,48 +3082,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00551/2026</t>
+          <t>ETO-RD-AR 00992/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5700322060</t>
+          <t>5710093157</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AL01054060</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-24 17:26</t>
+          <t>2026-06-18 17:27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>242.8</v>
+        <v>1031.7</v>
       </c>
       <c r="H37" t="n">
-        <v>10.1</v>
+        <v>43</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20264177286410</t>
+          <t>20264369657199</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-03-13 17:12</t>
+          <t>2026-05-06 10:58</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3132,11 +3132,11 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
+          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3151,61 +3151,61 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00305/2026</t>
+          <t>DG-RD-PO 00158/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5710633094</t>
+          <t>5710045026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PEIXE</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LD01066094</t>
+          <t>LD03046026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-07 15:40</t>
+          <t>2026-02-03 21:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>243.4</v>
+        <v>1197.3</v>
       </c>
       <c r="H38" t="n">
-        <v>10.1</v>
+        <v>49.9</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20264186017601</t>
+          <t>20254024629802</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-03-17 19:03</t>
+          <t>2025-12-15 19:26</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CONDUTOR DE AT</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>transformador e para raio queimado acesso livre levar porta fusivel da 34,5kv</t>
+          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3220,53 +3220,53 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00214/2026</t>
+          <t>ETO-RD-GU 00390/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5700230116</t>
+          <t>5700039076</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PINDORAMA DO TOCANTINS</t>
+          <t>DUERE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LD03046026</t>
+          <t>LD02040003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-23 13:59</t>
+          <t>2026-03-26 10:34</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>243.7</v>
+        <v>1339.2</v>
       </c>
       <c r="H39" t="n">
-        <v>10.2</v>
+        <v>55.8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20264175511481</t>
+          <t>20264106378753</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-03-12 15:36</t>
+          <t>2026-01-29 10:38</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3289,48 +3289,48 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00034/2026</t>
+          <t>DG-RD-PO 00178/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5700867040</t>
+          <t>5700861026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARAGOMINAS</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-01-08 10:53</t>
+          <t>2026-02-11 23:46</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>289.9</v>
+        <v>1379.7</v>
       </c>
       <c r="H40" t="n">
-        <v>12.1</v>
+        <v>57.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20254051242939</t>
+          <t>20254025938342</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-12-26 18:28</t>
+          <t>2025-12-15 20:15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
+          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3358,48 +3358,48 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00238/2026</t>
+          <t>ENC-RD-PS 00376/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5710058153</t>
+          <t>5700368012</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BERNARDO SAYAO</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-16 12:35</t>
+          <t>2026-03-20 18:48</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>399.9</v>
+        <v>1519.7</v>
       </c>
       <c r="H41" t="n">
-        <v>16.7</v>
+        <v>63.3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20264112068933</t>
+          <t>20264084825759</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-01-30 17:52</t>
+          <t>2026-01-15 13:28</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3427,48 +3427,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00484/2026</t>
+          <t>ENC-RD-PS 00481/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5702075022</t>
+          <t>5701214055</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-15 13:37</t>
+          <t>2026-04-28 09:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>506.3</v>
+        <v>1654.3</v>
       </c>
       <c r="H42" t="n">
-        <v>21.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20264133539002</t>
+          <t>20264130135232</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-02-22 07:31</t>
+          <t>2026-02-17 17:16</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
+          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3496,48 +3496,48 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00188/2026</t>
+          <t>ETO-RD-GU 00429/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5739688157</t>
+          <t>5710235032</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD01008032</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-01-30 11:44</t>
+          <t>2026-04-06 10:49</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>595.4</v>
+        <v>2273.2</v>
       </c>
       <c r="H43" t="n">
-        <v>24.8</v>
+        <v>94.7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20264066876544</t>
+          <t>20264060776927</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-01-05 14:21</t>
+          <t>2025-12-31 16:09</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
+          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>DANO(S) CAUSADO POR TERCEIROS</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3565,48 +3565,48 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00463/2026</t>
+          <t>DOLP-RD-PA 00643/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5701543077</t>
+          <t>5746488122</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AL01042078</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-11 21:10</t>
+          <t>2026-06-07 14:26</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>607.3</v>
+        <v>2781.8</v>
       </c>
       <c r="H44" t="n">
-        <v>25.3</v>
+        <v>115.9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20264127861374</t>
+          <t>20264123982556</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-02-13 18:53</t>
+          <t>2026-02-11 08:34</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3615,16 +3615,16 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
+          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3634,61 +3634,61 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00008/2026</t>
+          <t>ENC-RD-PS 00116/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5700188046</t>
+          <t>5700056149</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>CASEARA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LD01056046</t>
+          <t>LD03414149</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-03 18:05</t>
+          <t>2026-01-23 09:10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>609.4</v>
+        <v>3801.2</v>
       </c>
       <c r="H45" t="n">
-        <v>25.4</v>
+        <v>158.4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20254011736926</t>
+          <t>20264575311120</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-12-08 14:48</t>
+          <t>2026-06-30 18:19</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700056149 ATS Bomba de agua na rdr de caseara - levar N3 completa  cruzetas do tr madeira id 47357781Leva dus cruzeta leva tres isoladores Bastao as mesma estao danificada</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3697,1391 +3697,80 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00023/2026</t>
+          <t>ENC-RD-PS 00601/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5700005195</t>
+          <t>5753306085</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>MONTE SANTO DO TOCANTINS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-05 12:18</t>
+          <t>2026-06-24 12:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>621.8</v>
+        <v>4362.4</v>
       </c>
       <c r="H46" t="n">
-        <v>25.9</v>
+        <v>181.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20254016315055</t>
+          <t>20254044245739</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-12-10 13:52</t>
+          <t>2025-12-24 13:44</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
+          <t>TRAFO QUEIMADO  5753306085 30KVA 34,5KV, QUE ATENDE GARIMPO. CARGAS A REVELIA</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00122/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>5710169006</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TOCANTINIA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LD05050008</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-01-25 10:13</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>7 a 30 dias</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>674.2</v>
-      </c>
-      <c r="H47" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20254052989150</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2025-12-27 12:21</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ETO-RD-AG 00117/2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>5700011032</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NOVO PLANALTO</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LD01008032</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-01-30 18:32</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>7 a 30 dias</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>690.6</v>
-      </c>
-      <c r="H48" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20264152604502</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-02-28 13:07</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>TRafo 5710001103 de 15KVA na 19.9KV com vazamento de oleo lLocal: Povoado Buriti na RDR de São MiguelAcesso livre</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>POSTE DANIFICADO</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00064/2026</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>5711513001</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PORTO NACIONAL</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>AL03062013</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-01-16 03:49</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>733</v>
-      </c>
-      <c r="H49" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20254025928206</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2025-12-15 14:53</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00992/2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>5710093157</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ARAGUANA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LD01095030</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-06-18 17:27</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1031.7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>43</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20264369657199</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-05-06 10:58</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00740/2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5720011053</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>XAMBIOA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LD01095030</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-04-24 18:40</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1073.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20264492383402</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:08</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>CHAVE FUSIVEL/RELIGADORA</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Segundo informações 053OP01, o trafo 5720011053 de 30kVA está queimado, para raio também está queimado, acesso bom para equipe de manutenção.</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ETO-RD-GR 00208/2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>5700360227</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>RECURSOLANDIA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LD01065015</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-02-09 17:48</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1101.7</v>
-      </c>
-      <c r="H52" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20264207824552</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-03-27 15:27</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>TRAFO 5700360227 QUEIMADO PARA RAIO TAMBÉM DE 5 KVA NA NA REDE 19,9 KV ACESSO BOM PARA CAMIONETE FOI FEITO TESTE AVAZIO COSTATADO QUEIMADO INSTALAR GRAMPO ESTRIBO E GLV</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ETO-RD-GR 00199/2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>5700062227</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>RECURSOLANDIA</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LD01065015</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-02-06 21:05</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1164.7</v>
-      </c>
-      <c r="H53" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20264205477008</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-03-27 09:49</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>trafo 5700062227 - 15KVA - 34,5KV acesso caminhonete - para raio queimado cliente josé Luiz da Silva - saninda de santo onofre 7 km a esquerda 4km ate local - fazenda Paciencia - UC 2994421-2 -- RDR Recursolandia</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00158/2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>5710045026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LD03046026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-02-03 21:03</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1197.3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20254024629802</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2025-12-15 19:26</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00390/2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>5700039076</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>DUERE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LD02040003</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:34</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1339.2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20264106378753</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-01-29 10:38</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00178/2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>5700861026</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LD02059122</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-02-11 23:46</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1379.7</v>
-      </c>
-      <c r="H56" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20254025938342</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2025-12-15 20:15</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>ETO-RD-DP 00115/2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>5740059263</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>RIO DA CONCEICAO</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LD01028074</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-02-08 11:01</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1436.7</v>
-      </c>
-      <c r="H57" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20264268802426</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-04-09 07:42</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Segundo informações da equipe de campo, o Trafo 5740059263 de 15kVA na tensão 19.9kV está queimado, levar para raio, pois no trafo não tinha para raio, fica na fazenda Bonanza.</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00376/2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>5700368012</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LD04062013</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-03-20 18:48</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1519.7</v>
-      </c>
-      <c r="H58" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20264084825759</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-01-15 13:28</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00481/2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>5701214055</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ARAGUACEMA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LD01434149</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-04-28 09:30</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1654.3</v>
-      </c>
-      <c r="H59" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20264130135232</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-02-17 17:16</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
-        </is>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00327/2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>5710158159</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>MURICILANDIA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LD03010004</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-02-17 10:55</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>2194.1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20264414902046</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-05-19 20:58</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>2</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Trafo: 5710158159 queimado 45kvaTensão: 34,5Para-raio: Queimado Endereço: IND FAZENDA TRES MARIAS, 0Equipe: 058op02Contato da equipe: 99265-4554</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00429/2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5710235032</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NOVO PLANALTO</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LD01008032</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-04-06 10:49</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>2273.2</v>
-      </c>
-      <c r="H61" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20264060776927</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2025-12-31 16:09</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
-        </is>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00061/2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>5744049021</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>PARANA</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LD02010021</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-01-13 15:22</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>2560.7</v>
-      </c>
-      <c r="H62" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20264347866409</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-04-30 08:06</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>transformador e para raio queimado</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00643/2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>5746488122</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>PALMAS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LD02059122</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-06-07 14:26</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>2781.8</v>
-      </c>
-      <c r="H63" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20264123982556</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-02-11 08:34</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00116/2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>5700056149</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>CASEARA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LD03414149</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-01-23 09:10</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>3801.2</v>
-      </c>
-      <c r="H64" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20264575311120</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-06-30 18:19</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700056149 ATS Bomba de agua na rdr de caseara - levar N3 completa  cruzetas do tr madeira id 47357781Leva dus cruzeta leva tres isoladores Bastao as mesma estao danificada</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00601/2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>5753306085</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>MONTE SANTO DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LD04062013</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-06-24 12:13</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>4362.4</v>
-      </c>
-      <c r="H65" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20254044245739</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2025-12-24 13:44</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>TRANSFORMADOR</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>3</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>TRAFO QUEIMADO  5753306085 30KVA 34,5KV, QUE ATENDE GARIMPO. CARGAS A REVELIA</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
-        </is>
-      </c>
-      <c r="O65" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O65"/>
+  <autoFilter ref="A3:O46"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>

--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$3:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$N$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 118 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
+          <t>Os 105 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19% dos 43</t>
+          <t>0% dos 30</t>
         </is>
       </c>
     </row>
@@ -580,11 +580,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>28% dos 43</t>
+          <t>30% dos 30</t>
         </is>
       </c>
     </row>
@@ -595,11 +595,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28% dos 43</t>
+          <t>37% dos 30</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16% dos 43</t>
+          <t>23% dos 30</t>
         </is>
       </c>
     </row>
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9% dos 43</t>
+          <t>10% dos 30</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4</v>
+        <v>24.9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.1</v>
+        <v>24.8</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>43 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
+          <t>30 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
         </is>
       </c>
     </row>
@@ -805,66 +805,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00458/2026</t>
+          <t>ETO-RD-GR 00387/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5700873122</t>
+          <t>5700018155</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AL04060122</t>
+          <t>LD02105019</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-15 15:02</t>
+          <t>2026-03-27 09:49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>24.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20264288661473</t>
+          <t>20264201727493</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-15 17:25</t>
+          <t>2026-03-25 14:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CHAVE FUSIVEL/RELIGADORA</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Transformador 5700873122 com vazamento de oleo grande proporção, potencia 112.5kva tensão 13.8 acesso livre a caminhao para raio bom, cabo aa/2,QP 120.</t>
+          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -874,48 +874,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00501/2026</t>
+          <t>ETO-RD-AR 00204/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5700105132</t>
+          <t>5723118030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAMPAIO</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LD02014045</t>
+          <t>LD02095030</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-13 07:19</t>
+          <t>2026-02-02 07:07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.9</v>
+        <v>35.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20264391468820</t>
+          <t>20264112025210</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-13 10:15</t>
+          <t>2026-01-30 08:49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Enviar equipe de manutenção para substituir trafo com vazamento de oleo na bucha secundária fase A - TRAFO 5700105132 - 5KVA-19.9KV</t>
+          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -943,48 +943,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00521/2026</t>
+          <t>ETO-RD-GR 00466/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5703327122</t>
+          <t>5710404111</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>PEQUIZEIRO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL05059122</t>
+          <t>LD03020023</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-02 18:51</t>
+          <t>2026-04-22 07:20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>38.6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20264354214073</t>
+          <t>20264307303463</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-02 22:20</t>
+          <t>2026-04-20 09:11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO 5703327122 COM VAZAMENTO DE OLEO, NA RDU DE PALMASPOTENCIA 45KVAQUADRA 206 SULOBS: SE POSSIVEL LEVAR UM TRAFO DE MAIOR POTENCIA</t>
+          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1012,53 +1012,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00493/2026</t>
+          <t>DOLP-RD-PA 00124/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5700265045</t>
+          <t>5711933122</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LD03014045</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-09 16:40</t>
+          <t>2026-01-25 12:35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>60.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20264378533481</t>
+          <t>20264092758229</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:10</t>
+          <t>2026-01-22 11:47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Constatado trafo 5700265045 de 10kVA na 19,9kV com vazamento de óleo. Melhores informações falar com Denismar 63 99972-2277</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1081,53 +1081,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00327/2026</t>
+          <t>DOLP-RD-PA 00177/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5700119039</t>
+          <t>5755307026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARAGUATINS</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AL01109039</t>
+          <t>LD06002091</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-24 16:47</t>
+          <t>2026-02-03 08:31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20264197663442</t>
+          <t>20264113211342</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-24 21:44</t>
+          <t>2026-01-30 11:15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TRAFO 5700119039 COM VAZAMENTO DE OLEO DE 75KVA DA 13.8. ACESSO LIVRE. TRAFO ENERGIZADO.</t>
+          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1150,48 +1150,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00209/2026</t>
+          <t>DG-RD-PO 00160/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5700237001</t>
+          <t>5753553037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>BREJINHO DE NAZARE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AL06072001</t>
+          <t>LD02001037</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-20 20:29</t>
+          <t>2026-02-04 09:56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14.8</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20264133314401</t>
+          <t>20264113024457</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-02-21 11:18</t>
+          <t>2026-01-30 10:22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1200,16 +1200,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO 5700237001 COM BUCHA PRIMARIA QUEBRADA PARA DEVIDAS TRATATIVAS COM EQUIPE DE MANUTENÇÃO.POTENCIA: 75 KVATENÇÃO: 13,8 KV ACESSO LIVRE</t>
+          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1219,66 +1219,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00324/2026</t>
+          <t>DOLP-RD-PA 00338/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5700006034</t>
+          <t>5704202122</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRESIDENTE KENNEDY</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL01073034</t>
+          <t>AL01099059</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-10 08:34</t>
+          <t>2026-03-10 16:17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>15.2</v>
+        <v>72.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20264171353629</t>
+          <t>20264165847819</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-10 23:48</t>
+          <t>2026-03-07 08:49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CONDUTOR DE BT</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>trafo 5700006034 com vazamento de oleo</t>
+          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1288,53 +1288,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00167/2026</t>
+          <t>ETO-RD-AR 00583/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5710328113</t>
+          <t>5700799193</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COUTO MAGALHAES</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LD03020023</t>
+          <t>LD03105019</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-02 10:49</t>
+          <t>2026-03-31 20:47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>até 24 horas</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>23.8</v>
+        <v>72.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20264116127370</t>
+          <t>20264208594801</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-02-03 10:36</t>
+          <t>2026-03-27 17:30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>trafo vazando oleo, levar porta fusivel</t>
+          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1357,27 +1357,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00387/2026</t>
+          <t>ETO-RD-AR 00774/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5700018155</t>
+          <t>5743290004</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LD02105019</t>
+          <t>AL01040004</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-27 09:49</t>
+          <t>2026-04-30 11:05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1386,24 +1386,24 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24.9</v>
+        <v>118.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20264201727493</t>
+          <t>20264326606216</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-03-25 14:00</t>
+          <t>2026-04-25 11:38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CHAVE FUSIVEL/RELIGADORA</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
+          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1426,66 +1426,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00487/2026</t>
+          <t>ETO-RD-AR 00268/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5700002253</t>
+          <t>5700382016</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHAPADA DE AREIA</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LD03062013</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:51</t>
+          <t>2026-02-08 11:20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28.2</v>
+        <v>234.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20264348037836</t>
+          <t>20264106536555</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-30 18:04</t>
+          <t>2026-01-27 19:13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>TR 5700002253MUITO VAZAMENTO DE OLEO 150 KVA34500PARA RAIO BOM ACESSO LIVRE013OP014 HEMINIO</t>
+          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1495,53 +1495,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00204/2026</t>
+          <t>ETO-RD-AR 00551/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5723118030</t>
+          <t>5700322060</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LD02095030</t>
+          <t>AL01054060</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-02 07:07</t>
+          <t>2026-03-24 17:26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35.8</v>
+        <v>242.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20264112025210</t>
+          <t>20264177286410</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-01-30 08:49</t>
+          <t>2026-03-13 17:12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1564,48 +1564,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00466/2026</t>
+          <t>ETO-RD-DP 00214/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5710404111</t>
+          <t>5700230116</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PEQUIZEIRO</t>
+          <t>PINDORAMA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LD03020023</t>
+          <t>LD03046026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-22 07:20</t>
+          <t>2026-03-23 13:59</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>38.6</v>
+        <v>243.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20264307303463</t>
+          <t>20264175511481</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-20 09:11</t>
+          <t>2026-03-12 15:36</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1614,11 +1614,11 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
+          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,48 +1633,48 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00124/2026</t>
+          <t>ETO-RD-AR 00034/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5711933122</t>
+          <t>5700867040</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>ARAGOMINAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-25 12:35</t>
+          <t>2026-01-08 10:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>60.7</v>
+        <v>289.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>12.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20264092758229</t>
+          <t>20254051242939</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-01-22 11:47</t>
+          <t>2025-12-26 18:28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1683,11 +1683,11 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
+          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1702,48 +1702,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00177/2026</t>
+          <t>ETO-RD-GR 00238/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5755307026</t>
+          <t>5710058153</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>BERNARDO SAYAO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LD06002091</t>
+          <t>LD01010153</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-03 08:31</t>
+          <t>2026-02-16 12:35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>64.40000000000001</v>
+        <v>399.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>16.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20264113211342</t>
+          <t>20264112068933</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-01-30 11:15</t>
+          <t>2026-01-30 17:52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
+          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1771,61 +1771,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00160/2026</t>
+          <t>ETO-RD-AR 00484/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5753553037</t>
+          <t>5702075022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BREJINHO DE NAZARE</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LD02001037</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-04 09:56</t>
+          <t>2026-03-15 13:37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>506.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>21.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20264113024457</t>
+          <t>20264133539002</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-01-30 10:22</t>
+          <t>2026-02-22 07:31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
+          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1840,61 +1840,61 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00338/2026</t>
+          <t>ETO-RD-AR 00188/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5704202122</t>
+          <t>5739688157</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL01099059</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-10 16:17</t>
+          <t>2026-01-30 11:44</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>72.2</v>
+        <v>595.4</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>24.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20264165847819</t>
+          <t>20264066876544</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-07 08:49</t>
+          <t>2026-01-05 14:21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CONDUTOR DE BT</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
+          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1909,66 +1909,66 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00583/2026</t>
+          <t>ETO-RD-AR 00463/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5700799193</t>
+          <t>5701543077</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>AL01042078</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-03-31 20:47</t>
+          <t>2026-03-11 21:10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>72.8</v>
+        <v>607.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>25.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20264208594801</t>
+          <t>20264127861374</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-27 17:30</t>
+          <t>2026-02-13 18:53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
+          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1978,130 +1978,130 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00774/2026</t>
+          <t>ENC-RD-PS 00008/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5743290004</t>
+          <t>5700188046</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AL01040004</t>
+          <t>LD01056046</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-30 11:05</t>
+          <t>2026-01-03 18:05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>118.9</v>
+        <v>609.4</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>25.4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20264326606216</t>
+          <t>20254011736926</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-25 11:38</t>
+          <t>2025-12-08 14:48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
+          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00278/2026</t>
+          <t>ETO-RD-GR 00023/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5700216064</t>
+          <t>5700005195</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRASILANDIA DO TOCANTINS</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>LD01065015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-23 20:17</t>
+          <t>2026-01-05 12:18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>142.1</v>
+        <v>621.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>25.9</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20264152703110</t>
+          <t>20254016315055</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-01 18:21</t>
+          <t>2025-12-10 13:52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>trafo 5700216064 com bucha danificada 15KVA 34,5KV para raio bom acesso livre. chacara firmeza - RDR BrasilandiaThiago Pires Moral - UC 3283572-0</t>
+          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2116,48 +2116,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00373/2026</t>
+          <t>DOLP-RD-PA 00122/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5700725023</t>
+          <t>5710169006</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>TOCANTINIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL02020023</t>
+          <t>LD05050008</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-23 18:37</t>
+          <t>2026-01-25 10:13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>165.5</v>
+        <v>674.2</v>
       </c>
       <c r="H23" t="n">
-        <v>6.9</v>
+        <v>28.1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20264213656808</t>
+          <t>20254052989150</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-30 16:08</t>
+          <t>2025-12-27 12:21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>por favor desloca equipe da manutenção pesada no trafo 5700725023 com vazamento oleo 112,5 kva na 13,8kv acesso bom urgente RDU</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2185,61 +2185,61 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00268/2026</t>
+          <t>DG-RD-PO 00064/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5700382016</t>
+          <t>5711513001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>PORTO NACIONAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>AL03062013</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-08 11:20</t>
+          <t>2026-01-16 03:49</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>234.3</v>
+        <v>733</v>
       </c>
       <c r="H24" t="n">
-        <v>9.800000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20264106536555</t>
+          <t>20254025928206</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-01-27 19:13</t>
+          <t>2025-12-15 14:53</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
+          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,48 +2254,48 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00551/2026</t>
+          <t>ETO-RD-AR 00992/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5700322060</t>
+          <t>5710093157</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AL01054060</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-24 17:26</t>
+          <t>2026-06-18 17:27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>242.8</v>
+        <v>1031.7</v>
       </c>
       <c r="H25" t="n">
-        <v>10.1</v>
+        <v>43</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20264177286410</t>
+          <t>20264369657199</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-03-13 17:12</t>
+          <t>2026-05-06 10:58</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2304,11 +2304,11 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
+          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2323,17 +2323,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00214/2026</t>
+          <t>DG-RD-PO 00158/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5700230116</t>
+          <t>5710045026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PINDORAMA DO TOCANTINS</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2343,41 +2343,41 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-23 13:59</t>
+          <t>2026-02-03 21:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>243.7</v>
+        <v>1197.3</v>
       </c>
       <c r="H26" t="n">
-        <v>10.2</v>
+        <v>49.9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20264175511481</t>
+          <t>20254024629802</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-03-12 15:36</t>
+          <t>2025-12-15 19:26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
+          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2392,48 +2392,48 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00034/2026</t>
+          <t>ETO-RD-GU 00390/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5700867040</t>
+          <t>5700039076</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARAGOMINAS</t>
+          <t>DUERE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD02040003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-01-08 10:53</t>
+          <t>2026-03-26 10:34</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>289.9</v>
+        <v>1339.2</v>
       </c>
       <c r="H27" t="n">
-        <v>12.1</v>
+        <v>55.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20254051242939</t>
+          <t>20264106378753</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-26 18:28</t>
+          <t>2026-01-29 10:38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2461,48 +2461,48 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00238/2026</t>
+          <t>DG-RD-PO 00178/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5710058153</t>
+          <t>5700861026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BERNARDO SAYAO</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-16 12:35</t>
+          <t>2026-02-11 23:46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>399.9</v>
+        <v>1379.7</v>
       </c>
       <c r="H28" t="n">
-        <v>16.7</v>
+        <v>57.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20264112068933</t>
+          <t>20254025938342</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-01-30 17:52</t>
+          <t>2025-12-15 20:15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
+          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2530,48 +2530,48 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00484/2026</t>
+          <t>ENC-RD-PS 00376/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5702075022</t>
+          <t>5700368012</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-15 13:37</t>
+          <t>2026-03-20 18:48</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>506.3</v>
+        <v>1519.7</v>
       </c>
       <c r="H29" t="n">
-        <v>21.1</v>
+        <v>63.3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20264133539002</t>
+          <t>20264084825759</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-02-22 07:31</t>
+          <t>2026-01-15 13:28</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2580,11 +2580,11 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2599,48 +2599,48 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00188/2026</t>
+          <t>ENC-RD-PS 00481/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5739688157</t>
+          <t>5701214055</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-30 11:44</t>
+          <t>2026-04-28 09:30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>595.4</v>
+        <v>1654.3</v>
       </c>
       <c r="H30" t="n">
-        <v>24.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20264066876544</t>
+          <t>20264130135232</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-01-05 14:21</t>
+          <t>2026-02-17 17:16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
+          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2668,48 +2668,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00463/2026</t>
+          <t>ETO-RD-GU 00429/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5701543077</t>
+          <t>5710235032</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AL01042078</t>
+          <t>LD01008032</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-11 21:10</t>
+          <t>2026-04-06 10:49</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>607.3</v>
+        <v>2273.2</v>
       </c>
       <c r="H31" t="n">
-        <v>25.3</v>
+        <v>94.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20264127861374</t>
+          <t>20264060776927</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-02-13 18:53</t>
+          <t>2025-12-31 16:09</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
+          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>DANO(S) CAUSADO POR TERCEIROS</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2737,48 +2737,48 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00008/2026</t>
+          <t>DOLP-RD-PA 00643/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5700188046</t>
+          <t>5746488122</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LD01056046</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-01-03 18:05</t>
+          <t>2026-06-07 14:26</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>609.4</v>
+        <v>2781.8</v>
       </c>
       <c r="H32" t="n">
-        <v>25.4</v>
+        <v>115.9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20254011736926</t>
+          <t>20264123982556</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-08 14:48</t>
+          <t>2026-02-11 08:34</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2787,11 +2787,11 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
+          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2800,977 +2800,80 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00023/2026</t>
+          <t>ENC-RD-PS 00601/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5700005195</t>
+          <t>5753306085</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>MONTE SANTO DO TOCANTINS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-05 12:18</t>
+          <t>2026-06-24 12:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>mais de 3 meses</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>621.8</v>
+        <v>4362.4</v>
       </c>
       <c r="H33" t="n">
-        <v>25.9</v>
+        <v>181.8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20254016315055</t>
+          <t>20254044245739</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-12-10 13:52</t>
+          <t>2025-12-24 13:44</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
+          <t>TRAFO QUEIMADO  5753306085 30KVA 34,5KV, QUE ATENDE GARIMPO. CARGAS A REVELIA</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00122/2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5710169006</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>TOCANTINIA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LD05050008</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-01-25 10:13</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>7 a 30 dias</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>674.2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20254052989150</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2025-12-27 12:21</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ETO-RD-AG 00117/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>5700011032</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NOVO PLANALTO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LD01008032</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-01-30 18:32</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>7 a 30 dias</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>690.6</v>
-      </c>
-      <c r="H35" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20264152604502</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-02-28 13:07</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>TRafo 5710001103 de 15KVA na 19.9KV com vazamento de oleo lLocal: Povoado Buriti na RDR de São MiguelAcesso livre</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>POSTE DANIFICADO</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00064/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>5711513001</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>PORTO NACIONAL</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>AL03062013</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-01-16 03:49</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>733</v>
-      </c>
-      <c r="H36" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20254025928206</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2025-12-15 14:53</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ETO-RD-AR 00992/2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>5710093157</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ARAGUANA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LD01095030</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-06-18 17:27</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1031.7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>43</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20264369657199</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-05-06 10:58</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00158/2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>5710045026</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LD03046026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-02-03 21:03</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1197.3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20254024629802</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2025-12-15 19:26</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00390/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>5700039076</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DUERE</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LD02040003</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:34</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>1339.2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20264106378753</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-01-29 10:38</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DG-RD-PO 00178/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>5700861026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LD02059122</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-02-11 23:46</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1379.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20254025938342</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2025-12-15 20:15</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00376/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>5700368012</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LD04062013</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-03-20 18:48</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1519.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20264084825759</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-01-15 13:28</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00481/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>5701214055</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ARAGUACEMA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LD01434149</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-04-28 09:30</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1 a 3 meses</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1654.3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20264130135232</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-02-17 17:16</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ETO-RD-GU 00429/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5710235032</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>NOVO PLANALTO</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LD01008032</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-04-06 10:49</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>2273.2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20264060776927</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2025-12-31 16:09</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DOLP-RD-PA 00643/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>5746488122</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PALMAS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LD02059122</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-06-07 14:26</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>2781.8</v>
-      </c>
-      <c r="H44" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20264123982556</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-02-11 08:34</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00116/2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>5700056149</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CASEARA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LD03414149</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-01-23 09:10</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>3801.2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20264575311120</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-06-30 18:19</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700056149 ATS Bomba de agua na rdr de caseara - levar N3 completa  cruzetas do tr madeira id 47357781Leva dus cruzeta leva tres isoladores Bastao as mesma estao danificada</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ENC-RD-PS 00601/2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>5753306085</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MONTE SANTO DO TOCANTINS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LD04062013</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-06-24 12:13</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>mais de 3 meses</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>4362.4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20254044245739</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2025-12-24 13:44</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>TRANSFORMADOR</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>3</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>TRAFO QUEIMADO  5753306085 30KVA 34,5KV, QUE ATENDE GARIMPO. CARGAS A REVELIA</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O46"/>
+  <autoFilter ref="A3:O33"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>

--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$3:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$N$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fora da janela'!$A$3:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ausentes da Crítica'!$A$3:$N$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 105 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
+          <t>Os 108 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0% dos 30</t>
+          <t>3% dos 31</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>30% dos 30</t>
+          <t>29% dos 31</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>37% dos 30</t>
+          <t>35% dos 31</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23% dos 30</t>
+          <t>23% dos 31</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10% dos 30</t>
+          <t>10% dos 31</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>30 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
+          <t>31 solicitações em que a Crítica registra defeito aberto NO PRÓPRIO transformador, em data que não cabe na janela desta SS. A distância é medida da abertura da SS até a borda mais próxima do intervalo inteiro da ocorrência — a régua da peneira. Ordenadas da mais perto para a mais longe.</t>
         </is>
       </c>
     </row>
@@ -805,66 +805,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00387/2026</t>
+          <t>ETO-RD-GU 00017/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5700018155</t>
+          <t>5701363094</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>PEIXE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LD02105019</t>
+          <t>LD01066094</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-27 09:49</t>
+          <t>2026-01-04 15:53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 a 7 dias</t>
+          <t>até 24 horas</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20264201727493</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-03-25 14:00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>CHAVE FUSIVEL/RELIGADORA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
+          <t>bucha secundaria queimada para raio queimado e chave fusivel com defeito 19,9kv</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -874,27 +862,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00204/2026</t>
+          <t>ETO-RD-GR 00387/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5723118030</t>
+          <t>5700018155</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LD02095030</t>
+          <t>LD02105019</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-02 07:07</t>
+          <t>2026-03-27 09:49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -903,24 +891,24 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35.8</v>
+        <v>24.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20264112025210</t>
+          <t>20264201727493</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-30 08:49</t>
+          <t>2026-03-25 14:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>CHAVE FUSIVEL/RELIGADORA</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -928,12 +916,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
+          <t>trafo 5700018155 com vazamento de óleo - 25KVA - 19,9KV - para raio queimado substituir poste 10/200 estrutura U1/S1 - danificado na base. RDU do Povoado Cicilândia RDR Palmeirante</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -943,27 +931,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00466/2026</t>
+          <t>ETO-RD-AR 00204/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5710404111</t>
+          <t>5723118030</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PEQUIZEIRO</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LD03020023</t>
+          <t>LD02095030</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-22 07:20</t>
+          <t>2026-02-02 07:07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -972,19 +960,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>38.6</v>
+        <v>35.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20264307303463</t>
+          <t>20264112025210</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-20 09:11</t>
+          <t>2026-01-30 08:49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,11 +981,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
+          <t>EQUIPE 030OP01TRAFO QUEIMADO 5723118030 potencia 10KVA tensão 34.5KV E RECUPERAR  BT ROMPIDAACESSO CAMINHONETE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1012,27 +1000,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00124/2026</t>
+          <t>ETO-RD-GR 00466/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5711933122</t>
+          <t>5710404111</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>PEQUIZEIRO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD03020023</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-25 12:35</t>
+          <t>2026-04-22 07:20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1041,24 +1029,24 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>60.7</v>
+        <v>38.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20264092758229</t>
+          <t>20264307303463</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-22 11:47</t>
+          <t>2026-04-20 09:11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1066,7 +1054,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
+          <t>TRAFO QUEIMADO DE 15KVA DA 19.9. PARA RAIOS QUEIMADO. ACESSO BOM. 01 CLIENTE PENALIZADO.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1081,27 +1069,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00177/2026</t>
+          <t>DOLP-RD-PA 00124/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5755307026</t>
+          <t>5711933122</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LD06002091</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-03 08:31</t>
+          <t>2026-01-25 12:35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1110,19 +1098,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>64.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20264113211342</t>
+          <t>20264092758229</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-01-30 11:15</t>
+          <t>2026-01-22 11:47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1131,11 +1119,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio da rede de 34,500kv para ser subistituido pela equipe de manutencão acesso livre cliente penalizado 01 equipe que atendeu 059op12 cel, 63985065407/992621690 favor agilizar o atendimento devido a reclamacão ser doo dia 24-01-2026 09:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1150,27 +1138,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00160/2026</t>
+          <t>DOLP-RD-PA 00177/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5753553037</t>
+          <t>5755307026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BREJINHO DE NAZARE</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LD02001037</t>
+          <t>LD06002091</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-04 09:56</t>
+          <t>2026-02-03 08:31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1179,32 +1167,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20264113024457</t>
+          <t>20264113211342</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-01-30 10:22</t>
+          <t>2026-01-30 11:15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
+          <t>Segundo informações da equipe 026OP03, o 5755307026 de 15kVA, tensão 19.9V, para raio está ok, acesso livre somente pra caminhonete.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1219,27 +1207,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00338/2026</t>
+          <t>DG-RD-PO 00160/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5704202122</t>
+          <t>5753553037</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>BREJINHO DE NAZARE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL01099059</t>
+          <t>LD02001037</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-10 16:17</t>
+          <t>2026-02-04 09:56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1248,32 +1236,32 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>72.2</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20264165847819</t>
+          <t>20264113024457</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-03-07 08:49</t>
+          <t>2026-01-30 10:22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CONDUTOR DE BT</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
+          <t>TRAFO 5753553037 E PARA RAIO QUEIMADO POTENCIA: 75KVA 34500ACESSO: LIVRE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1288,27 +1276,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00583/2026</t>
+          <t>DOLP-RD-PA 00338/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5700799193</t>
+          <t>5704202122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>AL01099059</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-31 20:47</t>
+          <t>2026-03-10 16:17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1317,32 +1305,32 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>72.8</v>
+        <v>72.2</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20264208594801</t>
+          <t>20264165847819</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-27 17:30</t>
+          <t>2026-03-07 08:49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>CONDUTOR DE BT</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
+          <t>Segue esse para substituição de TF queimado (bucha do TF) 5704202122ID: 50688272</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1357,27 +1345,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00774/2026</t>
+          <t>ETO-RD-AR 00583/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5743290004</t>
+          <t>5700799193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL01040004</t>
+          <t>LD03105019</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-30 11:05</t>
+          <t>2026-03-31 20:47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1386,24 +1374,24 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>118.9</v>
+        <v>72.8</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20264326606216</t>
+          <t>20264208594801</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-25 11:38</t>
+          <t>2026-03-27 17:30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1411,12 +1399,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
+          <t>Trafo 5700799193  15kvaPara-raio: Queimado Endereço: fazenda arueira saindo povoado RanchariaEquipe: 193op02</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1426,66 +1414,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00268/2026</t>
+          <t>ETO-RD-AR 00774/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5700382016</t>
+          <t>5743290004</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>AL01040004</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-08 11:20</t>
+          <t>2026-04-30 11:05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7 a 30 dias</t>
+          <t>1 a 7 dias</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>234.3</v>
+        <v>118.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20264106536555</t>
+          <t>20264326606216</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-01-27 19:13</t>
+          <t>2026-04-25 11:38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CAUSA NAO IDENTIFICADA</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
+          <t>Trafo 5743290004  75kvaAcesso: livra na RDU de AraguainaSetor: Costa esmeraldoEquipe: de manutenção encontrou o defeito vazando oléo e saindo fumaça pela bucha que foi feito reparo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1495,27 +1483,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00551/2026</t>
+          <t>ETO-RD-AR 00268/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5700322060</t>
+          <t>5700382016</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AL01054060</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-24 17:26</t>
+          <t>2026-02-08 11:20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1524,32 +1512,32 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>242.8</v>
+        <v>234.3</v>
       </c>
       <c r="H14" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20264177286410</t>
+          <t>20264106536555</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-03-13 17:12</t>
+          <t>2026-01-27 19:13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>CAUSA NAO IDENTIFICADA</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
+          <t>trafo queimado, caiu uma descarga no mesmo pararaio queimado</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1564,27 +1552,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00214/2026</t>
+          <t>ETO-RD-AR 00551/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5700230116</t>
+          <t>5700322060</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PINDORAMA DO TOCANTINS</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LD03046026</t>
+          <t>AL01054060</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-23 13:59</t>
+          <t>2026-03-24 17:26</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1593,32 +1581,32 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>243.7</v>
+        <v>242.8</v>
       </c>
       <c r="H15" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20264175511481</t>
+          <t>20264177286410</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-03-12 15:36</t>
+          <t>2026-03-13 17:12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE NOVA OLINDA, TRAFO DE 15KVA NA REDE DE 7.8KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,27 +1621,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00034/2026</t>
+          <t>ETO-RD-DP 00214/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5700867040</t>
+          <t>5700230116</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARAGOMINAS</t>
+          <t>PINDORAMA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD03046026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-08 10:53</t>
+          <t>2026-03-23 13:59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1662,32 +1650,32 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>289.9</v>
+        <v>243.7</v>
       </c>
       <c r="H16" t="n">
-        <v>12.1</v>
+        <v>10.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20254051242939</t>
+          <t>20264175511481</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-26 18:28</t>
+          <t>2026-03-12 15:36</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>TRANSFORMADOR</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
+          <t>TRANSFORMADOR QUEIMADO 5700230116 5kva e para raio queimado na 19,9 acesso caminhonete  equipe 096op01 992400102</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1702,27 +1690,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00238/2026</t>
+          <t>ETO-RD-AR 00034/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5710058153</t>
+          <t>5700867040</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BERNARDO SAYAO</t>
+          <t>ARAGOMINAS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-16 12:35</t>
+          <t>2026-01-08 10:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1731,19 +1719,19 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>399.9</v>
+        <v>289.9</v>
       </c>
       <c r="H17" t="n">
-        <v>16.7</v>
+        <v>12.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20264112068933</t>
+          <t>20254051242939</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-01-30 17:52</t>
+          <t>2025-12-26 18:28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1756,7 +1744,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
+          <t>Trafo 5700867040 15kvaTensão: 19.9Equipe: 058op03Endereço: IND ASSENTAMEN P.A. REUNIDAS, 0 - LOTE 37</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1771,27 +1759,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00484/2026</t>
+          <t>ETO-RD-GR 00238/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5702075022</t>
+          <t>5710058153</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>BERNARDO SAYAO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD01010153</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-15 13:37</t>
+          <t>2026-02-16 12:35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1800,19 +1788,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>506.3</v>
+        <v>399.9</v>
       </c>
       <c r="H18" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20264133539002</t>
+          <t>20264112068933</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-02-22 07:31</t>
+          <t>2026-01-30 17:52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1821,11 +1809,11 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
+          <t>TR-5710058153 Queimadopara raios QUEIMADO potência 15kvatensão 34,5kvacesso CAMINHONETEequipe 025op01 tel-63992452770</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1840,27 +1828,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00188/2026</t>
+          <t>ETO-RD-AR 00484/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5739688157</t>
+          <t>5702075022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-01-30 11:44</t>
+          <t>2026-03-15 13:37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1869,19 +1857,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>595.4</v>
+        <v>506.3</v>
       </c>
       <c r="H19" t="n">
-        <v>24.8</v>
+        <v>21.1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20264066876544</t>
+          <t>20264133539002</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-01-05 14:21</t>
+          <t>2026-02-22 07:31</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1890,11 +1878,11 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
+          <t>TRAFO 5702075022 5KVA 34.5KVCHACARA SAO MIGUELACESSO PARA CAMINHONETE</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1909,27 +1897,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00463/2026</t>
+          <t>ETO-RD-AR 00188/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5701543077</t>
+          <t>5739688157</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL01042078</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-03-11 21:10</t>
+          <t>2026-01-30 11:44</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1938,19 +1926,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>607.3</v>
+        <v>595.4</v>
       </c>
       <c r="H20" t="n">
-        <v>25.3</v>
+        <v>24.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20264127861374</t>
+          <t>20264066876544</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-02-13 18:53</t>
+          <t>2026-01-05 14:21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1959,16 +1947,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
+          <t>TRAFO QUEIMADO 5739688157 pararaio queimado acesso caminhonete</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1978,27 +1966,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00008/2026</t>
+          <t>ETO-RD-AR 00463/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5700188046</t>
+          <t>5701543077</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOVA ROSALANDIA</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LD01056046</t>
+          <t>AL01042078</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-01-03 18:05</t>
+          <t>2026-03-11 21:10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2007,19 +1995,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>609.4</v>
+        <v>607.3</v>
       </c>
       <c r="H21" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20254011736926</t>
+          <t>20264127861374</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-08 14:48</t>
+          <t>2026-02-13 18:53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2028,46 +2016,46 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
+          <t>TR-5701543077 vazando oleo para raios bompotência 5kvatensão 34,5kvacesso livreequipe 077op02 tel-63992409718</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00023/2026</t>
+          <t>ENC-RD-PS 00008/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5700005195</t>
+          <t>5700188046</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>NOVA ROSALANDIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>LD01056046</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-01-05 12:18</t>
+          <t>2026-01-03 18:05</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2076,67 +2064,67 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>621.8</v>
+        <v>609.4</v>
       </c>
       <c r="H22" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20254016315055</t>
+          <t>20254011736926</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-10 13:52</t>
+          <t>2025-12-08 14:48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
+          <t>MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
+          <t>TR 5700188046 QUEIMADO 30KVAPARA RAIO DANIFICADO ACESSO LIVRET 34500013OP14</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00122/2026</t>
+          <t>ETO-RD-GR 00023/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5710169006</t>
+          <t>5700005195</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TOCANTINIA</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LD05050008</t>
+          <t>LD01065015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-01-25 10:13</t>
+          <t>2026-01-05 12:18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2145,24 +2133,24 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>674.2</v>
+        <v>621.8</v>
       </c>
       <c r="H23" t="n">
-        <v>28.1</v>
+        <v>25.9</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20254052989150</t>
+          <t>20254016315055</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-27 12:21</t>
+          <t>2025-12-10 13:52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>MEIO AMBIENTE</t>
+          <t>DESLIGAMENTO SEM PROGRAMACAO PREVIA</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -2170,12 +2158,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
+          <t>Trafo: 5700005195 vazamento de oleo Potencia: 75 KVATensão: 34,5 KV Para raio: queimado Acesso: livre     Equipe: 227op01 (63) 99999-8761/99928-1276Obs. tem que tracar estrutura N1 completa e chave 34,5 KV que atende o trafo. substituir cabos do pirastique.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2185,48 +2173,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00064/2026</t>
+          <t>DOLP-RD-PA 00122/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5711513001</t>
+          <t>5710169006</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PORTO NACIONAL</t>
+          <t>TOCANTINIA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AL03062013</t>
+          <t>LD05050008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-01-16 03:49</t>
+          <t>2026-01-25 10:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1 a 3 meses</t>
+          <t>7 a 30 dias</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>733</v>
+        <v>674.2</v>
       </c>
       <c r="H24" t="n">
-        <v>30.5</v>
+        <v>28.1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20254025928206</t>
+          <t>20254052989150</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-15 14:53</t>
+          <t>2025-12-27 12:21</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2239,7 +2227,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
+          <t>segue ss de 01 trafo de 15 kvar e 01 para raio queimado da rede de 34.500kv para ser subistituido pela equipe de manutencão cliente penalizado 01 equipe que atendeu 006op01 cel, 63992363662/992379486 acesso livre favor agilizar o atendimento</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,27 +2242,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00992/2026</t>
+          <t>DG-RD-PO 00064/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5710093157</t>
+          <t>5711513001</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ARAGUANA</t>
+          <t>PORTO NACIONAL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>AL03062013</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-18 17:27</t>
+          <t>2026-01-16 03:49</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2283,19 +2271,19 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1031.7</v>
+        <v>733</v>
       </c>
       <c r="H25" t="n">
-        <v>43</v>
+        <v>30.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20264369657199</t>
+          <t>20254025928206</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-05-06 10:58</t>
+          <t>2025-12-15 14:53</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2304,11 +2292,11 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
+          <t>Segue nota para envia equipe manutenção substituir Trafo 5711513001 de 10kva e para-raio avariado, Tensão 7,9kv, Rural de Porto Nacional Assentamento P.A. Pau Darco, Chac. Duas Irmãs, Acesso para camionete 4x4.Obs. Informação da equipe 001OP11 Trafo não Funcionando.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2323,27 +2311,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00158/2026</t>
+          <t>ETO-RD-AR 00992/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5710045026</t>
+          <t>5710093157</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>ARAGUANA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LD03046026</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-03 21:03</t>
+          <t>2026-06-18 17:27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2352,19 +2340,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1197.3</v>
+        <v>1031.7</v>
       </c>
       <c r="H26" t="n">
-        <v>49.9</v>
+        <v>43</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20254024629802</t>
+          <t>20264369657199</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-15 19:26</t>
+          <t>2026-05-06 10:58</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2373,11 +2361,11 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
+          <t>Trafo 5710093157  45kva queimadoPara-raio: QueimadoAcesso: livreEndereço: IND FAZENDA BARRA DO RIO LONTRA, 0Equipe: 030op01</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2392,27 +2380,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00390/2026</t>
+          <t>DG-RD-PO 00158/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5700039076</t>
+          <t>5710045026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DUERE</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LD02040003</t>
+          <t>LD03046026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-26 10:34</t>
+          <t>2026-02-03 21:03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2421,19 +2409,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1339.2</v>
+        <v>1197.3</v>
       </c>
       <c r="H27" t="n">
-        <v>55.8</v>
+        <v>49.9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20264106378753</t>
+          <t>20254024629802</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-01-29 10:38</t>
+          <t>2025-12-15 19:26</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2442,11 +2430,11 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
+          <t>TR 571004502615KVATENSAO 19,9PARA RAIO DANIFICADO ACESSO LIVRE 026OP01</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2461,27 +2449,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DG-RD-PO 00178/2026</t>
+          <t>ETO-RD-GU 00390/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5700861026</t>
+          <t>5700039076</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PONTE ALTA DO TOCANTINS</t>
+          <t>DUERE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD02040003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-11 23:46</t>
+          <t>2026-03-26 10:34</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2490,19 +2478,19 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1379.7</v>
+        <v>1339.2</v>
       </c>
       <c r="H28" t="n">
-        <v>57.5</v>
+        <v>55.8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20254025938342</t>
+          <t>20264106378753</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-15 20:15</t>
+          <t>2026-01-29 10:38</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2511,11 +2499,11 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
+          <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE DUERE, TRAFO DE 15KVA NA REDE DE 19.9KV, PARA RAIO QUEIMADO E ACESSO LIVRE.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2530,27 +2518,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00376/2026</t>
+          <t>DG-RD-PO 00178/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5700368012</t>
+          <t>5700861026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIVINOPOLIS DO TOCANTINS</t>
+          <t>PONTE ALTA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LD04062013</t>
+          <t>LD02059122</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-20 18:48</t>
+          <t>2026-02-11 23:46</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2559,19 +2547,19 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1519.7</v>
+        <v>1379.7</v>
       </c>
       <c r="H29" t="n">
-        <v>63.3</v>
+        <v>57.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20264084825759</t>
+          <t>20254025938342</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-01-15 13:28</t>
+          <t>2025-12-15 20:15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2584,7 +2572,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
+          <t>Trafo 5700861026 de 15kva e para-raio queimado, Tensão 19,9kv, Acesso para camionete 4x, Rural de Ponte Alta, faz. IND FAZENDA PRODUCAO, 0 - LPT-14877 FAZ PRODUCAO</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2599,27 +2587,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00481/2026</t>
+          <t>ENC-RD-PS 00376/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5701214055</t>
+          <t>5700368012</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARAGUACEMA</t>
+          <t>DIVINOPOLIS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LD01434149</t>
+          <t>LD04062013</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-28 09:30</t>
+          <t>2026-03-20 18:48</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2628,19 +2616,19 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1654.3</v>
+        <v>1519.7</v>
       </c>
       <c r="H30" t="n">
-        <v>68.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20264130135232</t>
+          <t>20264084825759</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-02-17 17:16</t>
+          <t>2026-01-15 13:28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2649,16 +2637,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
+          <t>Segue ss para tratativa com equipe de manutençao o quanto antessubstituir trafo 5700368012 queimado na rdr de divinopoles</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2668,48 +2656,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00429/2026</t>
+          <t>ENC-RD-PS 00481/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5710235032</t>
+          <t>5701214055</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NOVO PLANALTO</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LD01008032</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-06 10:49</t>
+          <t>2026-04-28 09:30</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>mais de 3 meses</t>
+          <t>1 a 3 meses</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2273.2</v>
+        <v>1654.3</v>
       </c>
       <c r="H31" t="n">
-        <v>94.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20264060776927</t>
+          <t>20264130135232</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-31 16:09</t>
+          <t>2026-02-17 17:16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2718,16 +2706,16 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
+          <t>TR 5701214055QUEIMADO ACESSO LIVRE CAMINHONETE 5KVATENSAO 34500PARA RAIO DANIFICADO 055OP01</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2737,27 +2725,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DOLP-RD-PA 00643/2026</t>
+          <t>ETO-RD-GU 00429/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5746488122</t>
+          <t>5710235032</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>NOVO PLANALTO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LD02059122</t>
+          <t>LD01008032</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-07 14:26</t>
+          <t>2026-04-06 10:49</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2766,19 +2754,19 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2781.8</v>
+        <v>2273.2</v>
       </c>
       <c r="H32" t="n">
-        <v>115.9</v>
+        <v>94.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20264123982556</t>
+          <t>20264060776927</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-02-11 08:34</t>
+          <t>2025-12-31 16:09</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2791,12 +2779,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
+          <t>trafo 5710235032 queimado  de 15 kva rdr de araguaçu tensão 19.9 kv acesso livre  e poste quebrado id 42840335 10/300 cabo AA / 4.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>DANO(S) CAUSADO POR TERCEIROS</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2806,74 +2794,143 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>DOLP-RD-PA 00643/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5746488122</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PALMAS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LD02059122</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-06-07 14:26</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>mais de 3 meses</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2781.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20264123982556</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-02-11 08:34</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MEIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>segue nota de trafo queimado, trafo 5745488122, trafo de 45kva, tensao 34,500kv, bitola caboAA / 2, para raio danificado, acesso livre, elo 2H. ramal do piabanha</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ENC-RD-PS 00601/2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>5753306085</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>MONTE SANTO DO TOCANTINS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>LD04062013</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>2026-06-24 12:13</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>mais de 3 meses</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G34" t="n">
         <v>4362.4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H34" t="n">
         <v>181.8</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>20254044245739</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2025-12-24 13:44</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>TRANSFORMADOR</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>TRAFO QUEIMADO  5753306085 30KVA 34,5KV, QUE ATENDE GARIMPO. CARGAS A REVELIA</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O33"/>
+  <autoFilter ref="A3:O34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
@@ -2887,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2909,7 +2966,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>75 solicitações em que a Crítica nunca registrou defeito aberto no próprio transformador, em data nenhuma dos sete meses. A coluna “Por que é ausente” separa os dois jeitos: o código não aparecer em papel nenhum, ou aparecer só como interrompido e manobrado — que é o que acontece com quem fica sem energia por defeito de outro equipamento. As colunas de ocorrência e de atendimento vêm escritas como “— nenhuma”: não existe registro, e mostrar “a ocorrência mais próxima” seria inventar vínculo.</t>
+          <t>77 solicitações em que a Crítica nunca registrou defeito aberto no próprio transformador, em data nenhuma dos sete meses. A coluna “Por que é ausente” separa os dois jeitos: o código não aparecer em papel nenhum, ou aparecer só como interrompido e manobrado — que é o que acontece com quem fica sem energia por defeito de outro equipamento. As colunas de ocorrência e de atendimento vêm escritas como “— nenhuma”: não existe registro, e mostrar “a ocorrência mais próxima” seria inventar vínculo.</t>
         </is>
       </c>
     </row>
@@ -4220,37 +4277,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00259/2026</t>
+          <t>ENC-RD-PS 00246/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5700191054</t>
+          <t>5720337055</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PUGMIL</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LD01056046</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-20 13:46</t>
+          <t>2026-02-17 15:45</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>manobrado em 1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4260,27 +4317,23 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>20264129266608</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264132739596 no ativo 0300191054 (20/02 08:43 a 22/02 07:41) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>substituir poste ID 47042587 10/300 estrutura do TR 5700191054 15KVA 19,9KV ACESSO BOM fotos anexadas na OS 20264131749370</t>
+          <t>TR 572033705515KVAPARA RAIO DANIFIFCADO 34500CAMINHONETE EQUIPE 055OP01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>DANO(S) CAUSADO POR TERCEIROS</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4290,27 +4343,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00358/2026</t>
+          <t>ENC-RD-PS 00259/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5700460055</t>
+          <t>5700191054</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARAGUACEMA</t>
+          <t>PUGMIL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LD01434149</t>
+          <t>LD01056046</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-17 18:55</t>
+          <t>2026-02-20 13:46</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4340,17 +4393,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264182680114 no ativo 5700411055 (17/03 09:48) — conferir número de série do equipamento retirado</t>
+          <t>Mesmo alimentador: ocorrência 20264132739596 no ativo 0300191054 (20/02 08:43 a 22/02 07:41) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TR 5763273055 15KVAPARA RAIO DANIFICADO ACESSO LIVRE PARA CAMINHONETE 055OP01 ESTEVE NO LOCAL TRAFO NAO AXISTE NO SISTEMA (ERRO CADASTRO) FICA PROX AO TR 5700460055MAIS INFORMAÇOES ENTRA EM CONTATO COM EQUIPE 055OP01</t>
+          <t>substituir poste ID 47042587 10/300 estrutura do TR 5700191054 15KVA 19,9KV ACESSO BOM fotos anexadas na OS 20264131749370</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>DANO(S) CAUSADO POR TERCEIROS</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4360,27 +4413,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00361/2026</t>
+          <t>ENC-RD-PS 00358/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5701007008</t>
+          <t>5700460055</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIRANORTE</t>
+          <t>ARAGUACEMA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AL02050008</t>
+          <t>LD01434149</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-03-19 10:47</t>
+          <t>2026-03-17 18:55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4410,12 +4463,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264186839193 no ativo 5700636008 (18/03 16:35 a 19/03 18:54) — número operativo provavelmente trocado</t>
+          <t>Mesma localidade: ocorrência 20264182680114 no ativo 5700411055 (17/03 09:48) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS:20264186004963Segue SS de TR queimado UC 9222677 e 3635120 TR não cadastrado 15KVA/7.9KV e para-raios queimados.Acesso livre.Localização: https://www.google.com/maps/search/?api=1&amp;query=-9.534713,-48.600728 SS aberta no TR 5701007008 porém o que está queimado é outro.FAZENDA BOA SORTE63984910222 </t>
+          <t>TR 5763273055 15KVAPARA RAIO DANIFICADO ACESSO LIVRE PARA CAMINHONETE 055OP01 ESTEVE NO LOCAL TRAFO NAO AXISTE NO SISTEMA (ERRO CADASTRO) FICA PROX AO TR 5700460055MAIS INFORMAÇOES ENTRA EM CONTATO COM EQUIPE 055OP01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -4430,27 +4483,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00438/2026</t>
+          <t>ENC-RD-PS 00361/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5701060070</t>
+          <t>5701007008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RIO SONO</t>
+          <t>MIRANORTE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LD01059122</t>
+          <t>AL02050008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-04-07 15:20</t>
+          <t>2026-03-19 10:47</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4480,12 +4533,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264262669137 no ativo 5752349092 (06/04 11:25 a 07/04 16:39) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264186839193 no ativo 5700636008 (18/03 16:35 a 19/03 18:54) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Segue SS de trafo 5701096007 queimado para devidas trativas com equipe de manutenção.Potencia 15 kvatensão 34.5kv para raio bomacesso livre OBS: trafo com erro de cadastro, o mesmo esta cadastrado na rededa 13.8 porem em campo esta ligado na rede da 34.5 kv. trafo fica localizado ao lado do trafo 57</t>
+          <t xml:space="preserve">OS:20264186004963Segue SS de TR queimado UC 9222677 e 3635120 TR não cadastrado 15KVA/7.9KV e para-raios queimados.Acesso livre.Localização: https://www.google.com/maps/search/?api=1&amp;query=-9.534713,-48.600728 SS aberta no TR 5701007008 porém o que está queimado é outro.FAZENDA BOA SORTE63984910222 </t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4500,27 +4553,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00546/2026</t>
+          <t>ENC-RD-PS 00438/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5701119075</t>
+          <t>5701060070</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DOIS IRMAOS DO TOCANTINS</t>
+          <t>RIO SONO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LD02050008</t>
+          <t>LD01059122</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-01 16:44</t>
+          <t>2026-04-07 15:20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4550,17 +4603,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264467783590 no ativo 3310079075 (01/06 13:00 a 01/06 21:28) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264262669137 no ativo 5752349092 (06/04 11:25 a 07/04 16:39) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5701119075 15KVA 34,5KV ACESSO BOM E PARA-RAIOS 075OP02</t>
+          <t>Segue SS de trafo 5701096007 queimado para devidas trativas com equipe de manutenção.Potencia 15 kvatensão 34.5kv para raio bomacesso livre OBS: trafo com erro de cadastro, o mesmo esta cadastrado na rededa 13.8 porem em campo esta ligado na rede da 34.5 kv. trafo fica localizado ao lado do trafo 57</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4570,27 +4623,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENC-RD-PS 00594/2026</t>
+          <t>ENC-RD-PS 00546/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5700417110</t>
+          <t>5701119075</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SANTA RITA DO TOCANTINS</t>
+          <t>DOIS IRMAOS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LD06047073</t>
+          <t>LD02050008</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-21 13:30</t>
+          <t>2026-06-01 16:44</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4615,22 +4668,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>Mesmo alimentador: ocorrência 20264467783590 no ativo 3310079075 (01/06 13:00 a 01/06 21:28) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRAFO 5700417110 DE 5 KVA NA REDE 19.9 KV QUEIMADO ACESSO BOM TROCAR E O POSTE DO TRAFO ID: 47152336 POIS O MESMO NÃO SUPORTA O TRAFO DE 15 E FINO E O POSTE ANTES DA CHAVE TRAFO 0300417110 NO ID: 68938875 PARA FAZER O SERVIÇO TEM ABRIR CHAVE LAMINA PROXIMO AO TRAFO 5700399073.</t>
+          <t>5701119075 15KVA 34,5KV ACESSO BOM E PARA-RAIOS 075OP02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>POSTE DANIFICADO</t>
+          <t>SUBST. TRAFO VAZANDO ÓLEO</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4640,37 +4693,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00164/2026</t>
+          <t>ENC-RD-PS 00594/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5700032103</t>
+          <t>5700417110</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAO MIGUEL DO TOCANTINS</t>
+          <t>SANTA RITA DO TOCANTINS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LD01076103</t>
+          <t>LD06047073</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-07 19:18</t>
+          <t>2026-06-21 13:30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>interrompido em 3 · manobrado em 3</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4688,15 +4741,19 @@
           <t>nada — sobe para campo</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trafo queimado</t>
+          <t>TRAFO 5700417110 DE 5 KVA NA REDE 19.9 KV QUEIMADO ACESSO BOM TROCAR E O POSTE DO TRAFO ID: 47152336 POIS O MESMO NÃO SUPORTA O TRAFO DE 15 E FINO E O POSTE ANTES DA CHAVE TRAFO 0300417110 NO ID: 68938875 PARA FAZER O SERVIÇO TEM ABRIR CHAVE LAMINA PROXIMO AO TRAFO 5700399073.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>POSTE DANIFICADO</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4706,27 +4763,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00249/2026</t>
+          <t>ETO-RD-AG 00164/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5700696045</t>
+          <t>5700032103</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>SAO MIGUEL DO TOCANTINS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LD03014045</t>
+          <t>LD01076103</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-03 12:18</t>
+          <t>2026-02-07 19:18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4736,7 +4793,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 2</t>
+          <t>interrompido em 3 · manobrado em 3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4757,7 +4814,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TROCA DE TRAFO 5700696045 QUEIMADO DE 30KVA DA 34.5 PARA RAIOS QUEIMADO. ACESSO BOMTROCAR JOGO DE CHAVESUBSTITUIR OS GLV'SLEVAR ROLDANA DA BT.</t>
+          <t>trafo queimado</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4772,37 +4829,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00437/2026</t>
+          <t>ETO-RD-AG 00249/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5700145002</t>
+          <t>5700696045</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TOCANTINOPOLIS</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AL01084002</t>
+          <t>LD03014045</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-22 08:06</t>
+          <t>2026-03-03 12:18</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4817,22 +4874,18 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264312501533 no ativo 5700323145 (21/04 13:28 a 22/04 10:13) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Segue SS de TR 5700145002 15KVA/7.9KV avariado com a bucha primária trincada e vazamento de óleo nas buchas secundárias.Acesso livre.UC 218774DISTRITO SANITARIO ESPECIAL INDIGENA TOCANTINSJoison 63 98404-8858</t>
+          <t>TROCA DE TRAFO 5700696045 QUEIMADO DE 30KVA DA 34.5 PARA RAIOS QUEIMADO. ACESSO BOMTROCAR JOGO DE CHAVESUBSTITUIR OS GLV'SLEVAR ROLDANA DA BT.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4842,27 +4895,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00489/2026</t>
+          <t>ETO-RD-AG 00437/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5701350103</t>
+          <t>5700145002</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAO MIGUEL DO TOCANTINS</t>
+          <t>TOCANTINOPOLIS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LD01014045</t>
+          <t>AL01084002</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-08 12:16</t>
+          <t>2026-04-22 08:06</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4892,17 +4945,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264270977071 no ativo 0322983103 (08/05 09:30) — conferir número de série do equipamento retirado</t>
+          <t>Mesmo alimentador: ocorrência 20264312501533 no ativo 5700323145 (21/04 13:28 a 22/04 10:13) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Segue SS de transformador 5701350103 Queimado Potencia 10 KVA Tensão: 19.9 KVAcesso livre Fazenda Jangada. Assentamento Camarão II</t>
+          <t>Segue SS de TR 5700145002 15KVA/7.9KV avariado com a bucha primária trincada e vazamento de óleo nas buchas secundárias.Acesso livre.UC 218774DISTRITO SANITARIO ESPECIAL INDIGENA TOCANTINSJoison 63 98404-8858</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -4912,27 +4965,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00508/2026</t>
+          <t>ETO-RD-AG 00489/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5701508039</t>
+          <t>5701350103</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARAGUATINS</t>
+          <t>SAO MIGUEL DO TOCANTINS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LD02109039</t>
+          <t>LD01014045</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-15 13:32</t>
+          <t>2026-05-08 12:16</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4962,12 +5015,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264399998658 no ativo 3301459039 (15/05 07:53 a 15/05 14:08) — número operativo provavelmente trocado</t>
+          <t>Mesma localidade: ocorrência 20264270977071 no ativo 0322983103 (08/05 09:30) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trafo queimado 5701508039 - 15KVA - 34,5KV - para raio queimado - acesso caminhonete. IND CHACARA BOA ESPERANCA - cliente: JUNHO ALVES DE SOUSA - 63992753298REF PROX AO PEQUENO E AO VALDINAR RDR ARAGUATINS</t>
+          <t>Segue SS de transformador 5701350103 Queimado Potencia 10 KVA Tensão: 19.9 KVAcesso livre Fazenda Jangada. Assentamento Camarão II</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4982,37 +5035,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETO-RD-AG 00545/2026</t>
+          <t>ETO-RD-AG 00508/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5700724045</t>
+          <t>5701508039</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AUGUSTINOPOLIS</t>
+          <t>ARAGUATINS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LD03014045</t>
+          <t>LD02109039</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-22 15:23</t>
+          <t>2026-05-15 13:32</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5027,18 +5080,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264399998658 no ativo 3301459039 (15/05 07:53 a 15/05 14:08) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>segue trafo 5700724045 com vazamento de oleo pot. 25 kva tensão 19,9kvpara-raio ruimacesso bom</t>
+          <t>trafo queimado 5701508039 - 15KVA - 34,5KV - para raio queimado - acesso caminhonete. IND CHACARA BOA ESPERANCA - cliente: JUNHO ALVES DE SOUSA - 63992753298REF PROX AO PEQUENO E AO VALDINAR RDR ARAGUATINS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5048,37 +5105,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00001/2026</t>
+          <t>ETO-RD-AG 00545/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5703016016</t>
+          <t>5700724045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>AUGUSTINOPOLIS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>LD03014045</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-01-02 10:17</t>
+          <t>2026-05-22 15:23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5093,22 +5150,18 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264062439510 no ativo 5700285080 (02/01 09:06 a 02/01 18:30) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SUBSTITUIR o Trafo 5703016016Lançar vão de rede de 100 metros , cabo AA / 4Instalar chave trafo ELO 0,5HAcesso livrePotencia de 15 kVA</t>
+          <t>segue trafo 5700724045 com vazamento de oleo pot. 25 kva tensão 19,9kvpara-raio ruimacesso bom</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5118,27 +5171,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00024/2026</t>
+          <t>ETO-RD-AR 00001/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5756806060</t>
+          <t>5703016016</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL02054060</t>
+          <t>LD02010004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-01-06 20:40</t>
+          <t>2026-01-02 10:17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5163,22 +5216,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>Mesmo alimentador: ocorrência 20264062439510 no ativo 5700285080 (02/01 09:06 a 02/01 18:30) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>TRAFO 5756806060 75KVA 13.8KV COM VAZAMENTO DE OLEO, ATENDE UMA ESCOLA DR. HELIO DE SOU BUENO NA RDU DE NOVA OLINDA</t>
+          <t>SUBSTITUIR o Trafo 5703016016Lançar vão de rede de 100 metros , cabo AA / 4Instalar chave trafo ELO 0,5HAcesso livrePotencia de 15 kVA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5188,27 +5241,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00081/2026</t>
+          <t>ETO-RD-AR 00024/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5704370057</t>
+          <t>5756806060</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>AL02054060</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-01-16 08:57</t>
+          <t>2026-01-06 20:40</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5233,22 +5286,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264085921158 no ativo 5710036159 (13/01 08:36 a 18/01 10:26) — número operativo provavelmente trocado</t>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Trafo 5704370057 15 kva queimadoTensão: 19.9Acesso: Livre Endereço: IND FAZENDA NOVO HORIZONTE, 0 - NOVO HORIZONTE 500M DA  PISTA</t>
+          <t>TRAFO 5756806060 75KVA 13.8KV COM VAZAMENTO DE OLEO, ATENDE UMA ESCOLA DR. HELIO DE SOU BUENO NA RDU DE NOVA OLINDA</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5258,12 +5311,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00118/2026</t>
+          <t>ETO-RD-AR 00081/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5700746004</t>
+          <t>5704370057</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5273,12 +5326,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-01-19 21:44</t>
+          <t>2026-01-16 08:57</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5308,12 +5361,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264088345566 no ativo 0301967022 (19/01 18:29 a 20/01 12:00) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264085921158 no ativo 5710036159 (13/01 08:36 a 18/01 10:26) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Trafo 5700746004 queimado 15kvaTensão: 19.9Acesso somente para caminhoneteEquipe: 004op08</t>
+          <t>Trafo 5704370057 15 kva queimadoTensão: 19.9Acesso: Livre Endereço: IND FAZENDA NOVO HORIZONTE, 0 - NOVO HORIZONTE 500M DA  PISTA</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5328,27 +5381,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00207/2026</t>
+          <t>ETO-RD-AR 00118/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5366985025</t>
+          <t>5700746004</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LD02010153</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-02 13:43</t>
+          <t>2026-01-19 21:44</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5378,12 +5431,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264115220045 no ativo 5700489136 (02/02 07:43 a 02/02 16:09) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264088345566 no ativo 0301967022 (19/01 18:29 a 20/01 12:00) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Boa noite,Favor enviar manutenção para subsitutir trafo 5366985025</t>
+          <t>Trafo 5700746004 queimado 15kvaTensão: 19.9Acesso somente para caminhoneteEquipe: 004op08</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5398,27 +5451,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00243/2026</t>
+          <t>ETO-RD-AR 00207/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5701262019</t>
+          <t>5366985025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LD01105019</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-04 18:47</t>
+          <t>2026-02-02 13:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5448,17 +5501,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264116079654 no ativo 5754932019 (03/02 12:19 a 05/02 16:24) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264115220045 no ativo 5700489136 (02/02 07:43 a 02/02 16:09) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Trafo 5701262019 avariado 15kvaTensão: 19.9Acesso livre</t>
+          <t>Boa noite,Favor enviar manutenção para subsitutir trafo 5366985025</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>POSTE DANIFICADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -5468,37 +5521,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00315/2026</t>
+          <t>ETO-RD-AR 00243/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5702058004</t>
+          <t>5701262019</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>FILADELFIA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL04096004</t>
+          <t>LD01105019</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-02-15 23:00</t>
+          <t>2026-02-04 18:47</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>interrompido em 2 · manobrado em 2</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5513,18 +5566,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264116079654 no ativo 5754932019 (03/02 12:19 a 05/02 16:24) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>trafo faltanto fase interno secundaria 5702058004 e com vazamento de oleopot 30kvatensao 34,5kvacesso caminhonetefazenda sao paulo GRANJA</t>
+          <t>Trafo 5701262019 avariado 15kvaTensão: 19.9Acesso livre</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>POSTE DANIFICADO</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -5534,37 +5591,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00415/2026</t>
+          <t>ETO-RD-AR 00315/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5700402060</t>
+          <t>5702058004</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NOVA OLINDA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AL01054060</t>
+          <t>AL04096004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-03 20:22</t>
+          <t>2026-02-15 23:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 2 · manobrado em 2</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5579,17 +5636,13 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264158896692 no ativo 64745653 (03/03 16:36 a 03/03 21:00) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TR-5700402060 vazando oleo para raios bompotência 10kvatensão 13,8kvacesso livreequipe 060op0102 tel-63992173964</t>
+          <t>trafo faltanto fase interno secundaria 5702058004 e com vazamento de oleopot 30kvatensao 34,5kvacesso caminhonetefazenda sao paulo GRANJA</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5604,37 +5657,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00434/2026</t>
+          <t>ETO-RD-AR 00415/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5710028040</t>
+          <t>5700402060</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARAGOMINAS</t>
+          <t>NOVA OLINDA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AL01006040</t>
+          <t>AL01054060</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-06 22:17</t>
+          <t>2026-03-03 20:22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5649,18 +5702,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264158896692 no ativo 64745653 (03/03 16:36 a 03/03 21:00) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Trafo 5710028040 Queimado Potencia:15 KVATensão: 13,8 KVPara raio: Queimado Acesso: CamionetaEquipe: 040op36 (63)992870450</t>
+          <t>TR-5700402060 vazando oleo para raios bompotência 10kvatensão 13,8kvacesso livreequipe 060op0102 tel-63992173964</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -5670,37 +5727,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00437/2026</t>
+          <t>ETO-RD-AR 00434/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5701771022</t>
+          <t>5710028040</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>ARAGOMINAS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>AL01006040</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-07 13:00</t>
+          <t>2026-03-06 22:17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5715,17 +5772,13 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264165948657 no ativo 5702442004 (07/03 10:14 a 07/03 14:35) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Trafo 5701771022 queimado 15kvaTensão: 34.5Acesso; somente para caminhonteEquipe: 004op27Endereço: Chacara Bela Vista</t>
+          <t>Trafo 5710028040 Queimado Potencia:15 KVATensão: 13,8 KVPara raio: Queimado Acesso: CamionetaEquipe: 040op36 (63)992870450</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5740,12 +5793,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00440/2026</t>
+          <t>ETO-RD-AR 00437/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5701182022</t>
+          <t>5701771022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5755,12 +5808,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LD04105019</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-08 11:28</t>
+          <t>2026-03-07 13:00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5790,17 +5843,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264166045879 no ativo 5701358022 (07/03 18:28) — conferir número de série do equipamento retirado</t>
+          <t>Mesmo alimentador: ocorrência 20264165948657 no ativo 5702442004 (07/03 10:14 a 07/03 14:35) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Bom dia Segue SSSenhores envia equipe na RDR de Babaçulândia para trocar poste e Trafo Trafo: 5701182022Poste: 10/200ID: 55662476Acesso:  Para caminhão e caminhoneteEndereço: Chácara Cantinho Pov. FarturãoOBS: Trocar poste e Trafo.</t>
+          <t>Trafo 5701771022 queimado 15kvaTensão: 34.5Acesso; somente para caminhonteEquipe: 004op27Endereço: Chacara Bela Vista</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>POSTE DANIFICADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -5810,27 +5863,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00468/2026</t>
+          <t>ETO-RD-AR 00440/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5301889004</t>
+          <t>5701182022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AL02096004</t>
+          <t>LD04105019</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-12 19:30</t>
+          <t>2026-03-08 11:28</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5860,17 +5913,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264174095227 no ativo 244R094 (12/03 17:06 a 12/03 20:11) — número operativo provavelmente trocado</t>
+          <t>Mesma localidade: ocorrência 20264166045879 no ativo 5701358022 (07/03 18:28) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Trafo 570188904 queimado 15kvaAcesso: Somente caminhonetePara-raio; Queimado Equipe: 004op26</t>
+          <t>Bom dia Segue SSSenhores envia equipe na RDR de Babaçulândia para trocar poste e Trafo Trafo: 5701182022Poste: 10/200ID: 55662476Acesso:  Para caminhão e caminhoneteEndereço: Chácara Cantinho Pov. FarturãoOBS: Trocar poste e Trafo.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>POSTE DANIFICADO</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -5880,37 +5933,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00504/2026</t>
+          <t>ETO-RD-AR 00468/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5752570159</t>
+          <t>5301889004</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MURICILANDIA</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LD03010004</t>
+          <t>AL02096004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-03-17 20:04</t>
+          <t>2026-03-12 19:30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5930,12 +5983,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264182949787 no ativo 5701421060 (17/03 09:54 a 17/03 22:01) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264174095227 no ativo 244R094 (12/03 17:06 a 12/03 20:11) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5752570159 30kva 34.5kv e para raioacesso livre</t>
+          <t>Trafo 570188904 queimado 15kvaAcesso: Somente caminhonetePara-raio; Queimado Equipe: 004op26</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5950,27 +6003,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00555/2026</t>
+          <t>ETO-RD-AR 00504/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5702259004</t>
+          <t>5752570159</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARAGUAINA</t>
+          <t>MURICILANDIA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LD02010153</t>
+          <t>LD03010004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-25 19:39</t>
+          <t>2026-03-17 20:04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5980,7 +6033,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 1</t>
+          <t>manobrado em 1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5995,13 +6048,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264182949787 no ativo 5701421060 (17/03 09:54 a 17/03 22:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>trafo queimado 5702259004 queimado 15 kv 19,9 kva para raio Bom acesso bom.fazenda Santa Tereza - UC 3165559-0 cliente: Persio de Freitas Vilela. RDR Arapoema</t>
+          <t>5752570159 30kva 34.5kv e para raioacesso livre</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6016,37 +6073,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00557/2026</t>
+          <t>ETO-RD-AR 00555/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5710138077</t>
+          <t>5702259004</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>ARAGUAINA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AL01042078</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-26 08:51</t>
+          <t>2026-03-25 19:39</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6061,22 +6118,18 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264201423278 no ativo 5720177077 (26/03 07:28 a 26/03 10:54) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>TR-5710138077 o mesmo não esta entregando a tensão adequadapara queimadopotência 10kvatensão 13,8kvacesso livreequipe 265op0 tel-63992212789</t>
+          <t>trafo queimado 5702259004 queimado 15 kv 19,9 kva para raio Bom acesso bom.fazenda Santa Tereza - UC 3165559-0 cliente: Persio de Freitas Vilela. RDR Arapoema</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -6086,27 +6139,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00576/2026</t>
+          <t>ETO-RD-AR 00557/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5100722193</t>
+          <t>5710138077</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CAMPOS LINDOS</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PS01112193</t>
+          <t>AL01042078</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-30 20:05</t>
+          <t>2026-03-26 08:51</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6136,17 +6189,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264225986217 no ativo 5700800193 (30/03 18:03) — conferir número de série do equipamento retirado</t>
+          <t>Mesmo alimentador: ocorrência 20264201423278 no ativo 5720177077 (26/03 07:28 a 26/03 10:54) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Segue trafo 5100722193 queimado, trafo atende RL 7900722193 SUPRIMENTO CEMAR, ACESSO LIVRETENSÃO 19,9KV POT. 15KVAPARA-RAIO BOMRELIGADOR ESTA SEM COMUNICAÇÃO DEVIDO PROBLEMA DO TRAFO NECESSITA URGENCIA</t>
+          <t>TR-5710138077 o mesmo não esta entregando a tensão adequadapara queimadopotência 10kvatensão 13,8kvacesso livreequipe 265op0 tel-63992212789</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -6156,27 +6209,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00582/2026</t>
+          <t>ETO-RD-AR 00576/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5710015080</t>
+          <t>5100722193</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>CAMPOS LINDOS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>PS01112193</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-31 20:03</t>
+          <t>2026-03-30 20:05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6206,12 +6259,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264243488362 no ativo 5700499080 (31/03 16:14 a 01/04 09:25) — número operativo provavelmente trocado</t>
+          <t>Mesma localidade: ocorrência 20264225986217 no ativo 5700800193 (30/03 18:03) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Trafo: 5710015080 QueimadoPotência: 15 KVARede: 34.5Pararaio: 34.5Acesso: só pra veículo traçadoSubstituir o mesmo pois está com a bucha primária quebrado por descarga atmosférica</t>
+          <t>Segue trafo 5100722193 queimado, trafo atende RL 7900722193 SUPRIMENTO CEMAR, ACESSO LIVRETENSÃO 19,9KV POT. 15KVAPARA-RAIO BOMRELIGADOR ESTA SEM COMUNICAÇÃO DEVIDO PROBLEMA DO TRAFO NECESSITA URGENCIA</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6226,27 +6279,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00658/2026</t>
+          <t>ETO-RD-AR 00582/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5761134022</t>
+          <t>5710015080</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BABACULANDIA</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LD05010004</t>
+          <t>LD02010004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-10 10:56</t>
+          <t>2026-03-31 20:03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6276,12 +6329,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264273385891 no ativo 5701014022 (09/04 22:50 a 10/04 11:13) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264243488362 no ativo 5700499080 (31/03 16:14 a 01/04 09:25) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>trafo 5761134022 75kva 34.5kv queimado</t>
+          <t>Trafo: 5710015080 QueimadoPotência: 15 KVARede: 34.5Pararaio: 34.5Acesso: só pra veículo traçadoSubstituir o mesmo pois está com a bucha primária quebrado por descarga atmosférica</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6296,27 +6349,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00690/2026</t>
+          <t>ETO-RD-AR 00658/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5766930077</t>
+          <t>5761134022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GOIATINS</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LD03105019</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-16 12:36</t>
+          <t>2026-04-10 10:56</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6346,17 +6399,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264292326563 no ativo 5701389077 (16/04 10:30 a 16/04 15:07) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264273385891 no ativo 5701014022 (09/04 22:50 a 10/04 11:13) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Boa tarde,Favor enviar manutenção para verificar trafo com vazamento de oleo no comutador de TAPTensão: 34,5Potencia: 15 kvaPara raio bomACESSO LIVREChacara Deus e Fiel</t>
+          <t>trafo 5761134022 75kva 34.5kv queimado</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -6366,27 +6419,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00700/2026</t>
+          <t>ETO-RD-AR 00690/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5710170025</t>
+          <t>5766930077</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ARAPOEMA</t>
+          <t>GOIATINS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LD02010153</t>
+          <t>LD03105019</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-17 14:38</t>
+          <t>2026-04-16 12:36</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6416,17 +6469,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264294400667 no ativo 5710135136 (17/04 08:41 a 17/04 15:29) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264292326563 no ativo 5701389077 (16/04 10:30 a 16/04 15:07) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>trafo 5710170025 queimado acesso bom para caminhonete 25kvaequipe 025op01</t>
+          <t>Boa tarde,Favor enviar manutenção para verificar trafo com vazamento de oleo no comutador de TAPTensão: 34,5Potencia: 15 kvaPara raio bomACESSO LIVREChacara Deus e Fiel</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -6436,37 +6489,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00742/2026</t>
+          <t>ETO-RD-AR 00700/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5710274030</t>
+          <t>5710170025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>ARAPOEMA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>LD02010153</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-25 18:08</t>
+          <t>2026-04-17 14:38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6486,17 +6539,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264326949336 no ativo 3300990016 (25/04 11:41 a 30/04 12:24) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264294400667 no ativo 5710135136 (17/04 08:41 a 17/04 15:29) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5710274030 transformador,esta com vazamento de óleo. Mas sem interrupção de Energia. 5 kVA. da 19.9 Local de livre acesso para caminhonete. Para raios bom</t>
+          <t>trafo 5710170025 queimado acesso bom para caminhonete 25kvaequipe 025op01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -6506,37 +6559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00763/2026</t>
+          <t>ETO-RD-AR 00702/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5710235080</t>
+          <t>5701086022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DARCINOPOLIS</t>
+          <t>BABACULANDIA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LD02010004</t>
+          <t>LD05010004</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-04-29 08:53</t>
+          <t>2026-04-18 17:12</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>manobrado em 1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6546,22 +6599,18 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>20264299796637</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264340843377 no ativo 5700331053 (27/04 08:49 a 29/04 17:00) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NOTA ABERTA PARA CORREÇÃO DA SS 751/2026 POIS O TRAFO QUE ESTAVA QUEIMADO E O 5710235080</t>
+          <t>Trafo 5701086022 Queimado Potencia: 15 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 022op02 (63)99255-6152Obs.: leva porta fusivel</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6576,17 +6625,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00773/2026</t>
+          <t>ETO-RD-AR 00742/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5700290030</t>
+          <t>5710274030</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6596,17 +6645,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-29 18:02</t>
+          <t>2026-04-25 18:08</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6631,12 +6680,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TRAFO QUEIMADO 5700920030POTENCIA: 5KVATENSÃO: 34,5KVACESSO BOM.PARA-RAIO QUEIMADO.FAZ. MORENA 1</t>
+          <t>5710274030 transformador,esta com vazamento de óleo. Mas sem interrupção de Energia. 5 kVA. da 19.9 Local de livre acesso para caminhonete. Para raios bom</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -6646,27 +6695,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00775/2026</t>
+          <t>ETO-RD-AR 00763/2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5700702019</t>
+          <t>5710235080</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FILADELFIA</t>
+          <t>DARCINOPOLIS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LD04105019</t>
+          <t>LD02010004</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-30 11:15</t>
+          <t>2026-04-29 08:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6691,17 +6740,17 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>Mesmo alimentador: ocorrência 20264340843377 no ativo 5700331053 (27/04 08:49 a 29/04 17:00) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Trafo 5700702019 15kvaAcesso: Livre Equipe:019op02Contato da equipe : 99242-6260</t>
+          <t>NOTA ABERTA PARA CORREÇÃO DA SS 751/2026 POIS O TRAFO QUE ESTAVA QUEIMADO E O 5710235080</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6716,17 +6765,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00818/2026</t>
+          <t>ETO-RD-AR 00773/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5710240030</t>
+          <t>5700290030</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>XAMBIOA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6736,7 +6785,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-08 19:27</t>
+          <t>2026-04-29 18:02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6766,17 +6815,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264375607668 no ativo 3310142053 (08/05 16:16 a 08/05 20:30) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264326949336 no ativo 3300990016 (25/04 11:41 a 30/04 12:24) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Trafo 5710240030 Vazamento de oleoPotencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 030op01 (63)98468-3634</t>
+          <t>TRAFO QUEIMADO 5700920030POTENCIA: 5KVATENSÃO: 34,5KVACESSO BOM.PARA-RAIO QUEIMADO.FAZ. MORENA 1</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -6786,37 +6835,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00872/2026</t>
+          <t>ETO-RD-AR 00775/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5710241016</t>
+          <t>5700702019</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WANDERLANDIA</t>
+          <t>FILADELFIA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LD01095030</t>
+          <t>LD04105019</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-17 17:55</t>
+          <t>2026-04-30 11:15</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6831,17 +6880,17 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264403490105 no ativo 5710176016 (16/05 18:23 a 17/05 18:20) — número operativo provavelmente trocado</t>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Trafo 5710241016 Queimado Potencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 004op26 (63)99214-9597</t>
+          <t>Trafo 5700702019 15kvaAcesso: Livre Equipe:019op02Contato da equipe : 99242-6260</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6856,37 +6905,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ETO-RD-AR 00987/2026</t>
+          <t>ETO-RD-AR 00818/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5700001058</t>
+          <t>5710240030</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SANTA FE DO ARAGUAIA</t>
+          <t>XAMBIOA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LD04010004</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-16 18:57</t>
+          <t>2026-05-08 19:27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>interrompido em 4 · manobrado em 4</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6901,44 +6950,52 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264375607668 no ativo 3310142053 (08/05 16:16 a 08/05 20:30) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>TRAFO 5700001058 75KVA 34.5KV COM VAZAMENTO DE OLEO OCASIONANDO INCENDIO NA BUCHA SECUNDARIARUA JOSE LINO DA SILVA, 0 - QD07 LT 04 PROX CARTORIO DE IMOVEIS RDU DE SANTA FÉ.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>Trafo 5710240030 Vazamento de oleoPotencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 030op01 (63)98468-3634</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO AVARIADO</t>
+        </is>
+      </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00248/2026</t>
+          <t>ETO-RD-AR 00872/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5700456038</t>
+          <t>5710241016</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TAGUATINGA</t>
+          <t>WANDERLANDIA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LD01414027</t>
+          <t>LD01095030</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-19 12:14</t>
+          <t>2026-05-17 17:55</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6968,12 +7025,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264302437570 no ativo 5710057038 (19/04 08:48 a 19/04 15:14) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264403490105 no ativo 5710176016 (16/05 18:23 a 17/05 18:20) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>trafo e para raio queimado 5700456038 15kva 19.9kv faz.oriente rdr de taguatinga equipe 038op01</t>
+          <t>Trafo 5710241016 Queimado Potencia: 10 KVATensão: 34,5 KVPara raio: Queimado Acesso: livreEquipe: 004op26 (63)99214-9597</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6988,37 +7045,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00052/2026</t>
+          <t>ETO-RD-AR 00987/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5741943048</t>
+          <t>5700001058</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>SANTA FE DO ARAGUAIA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LD02038009</t>
+          <t>LD04010004</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-09 18:59</t>
+          <t>2026-06-16 18:57</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 4 · manobrado em 4</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7033,62 +7090,54 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264070942400 no ativo 5700193048 (09/01 15:23 a 10/01 15:16) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>trafo queimado 5710088048, porem em campo esta o trafo 5741943048112.5 kVAacesso livre pararaio queimadoequipe 009op01- 63999201531</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
-        </is>
-      </c>
+          <t>TRAFO 5700001058 75KVA 34.5KV COM VAZAMENTO DE OLEO OCASIONANDO INCENDIO NA BUCHA SECUNDARIARUA JOSE LINO DA SILVA, 0 - QD07 LT 04 PROX CARTORIO DE IMOVEIS RDU DE SANTA FÉ.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00095/2026</t>
+          <t>ETO-RD-DP 00248/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5700396048</t>
+          <t>5700456038</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FORTALEZA DO TABOCAO</t>
+          <t>TAGUATINGA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LD02038009</t>
+          <t>LD01414027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-16 16:33</t>
+          <t>2026-04-19 12:14</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>manobrado em 1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7103,17 +7152,17 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>Mesmo alimentador: ocorrência 20264302437570 no ativo 5710057038 (19/04 08:48 a 19/04 15:14) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Trafo: 5700396048 Avariado Potencia: 15 KVATensão: 34,5kPara raio: queimado Acesso: Camioneta   Equipe: 009op02 (63)99983-3829Obs. trafo esta com tensão baixa em uma das buchas.</t>
+          <t>trafo e para raio queimado 5700456038 15kva 19.9kv faz.oriente rdr de taguatinga equipe 038op01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7128,27 +7177,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00140/2026</t>
+          <t>ETO-RD-GR 00052/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5700922009</t>
+          <t>5741943048</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GUARAI</t>
+          <t>FORTALEZA DO TABOCAO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LD04038009</t>
+          <t>LD02038009</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-28 20:04</t>
+          <t>2026-01-09 18:59</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7178,12 +7227,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264105160221 no ativo 5700923009 (28/01 19:38 a 29/01 13:05) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264070942400 no ativo 5700193048 (09/01 15:23 a 10/01 15:16) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TR-5700922009 Queimadopara raios queiamado potência 10kvatensão 34,5kvacesso livreequipe 009op01 tel-63984566867</t>
+          <t>trafo queimado 5710088048, porem em campo esta o trafo 5741943048112.5 kVAacesso livre pararaio queimadoequipe 009op01- 63999201531</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7198,27 +7247,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00174/2026</t>
+          <t>ETO-RD-GR 00095/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5747088104</t>
+          <t>5700396048</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BOM JESUS DO TOCANTINS</t>
+          <t>FORTALEZA DO TABOCAO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LD01065015</t>
+          <t>LD02038009</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-03 13:24</t>
+          <t>2026-01-16 16:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7243,17 +7292,17 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264113090887 no ativo 5728426129 (31/01 10:20 a 04/02 06:20) — número operativo provavelmente trocado</t>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>trafo queimado 5747088104 - 15KVA - 34,5KV - Acesso caminhonete - para raio queimadofazenda conquista - cliente Jose Reis Amario da Silva tel. 9.92521087 rdr Bom Jesus do Tocantins</t>
+          <t>Trafo: 5700396048 Avariado Potencia: 15 KVATensão: 34,5kPara raio: queimado Acesso: Camioneta   Equipe: 009op02 (63)99983-3829Obs. trafo esta com tensão baixa em uma das buchas.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7268,27 +7317,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00189/2026</t>
+          <t>ETO-RD-GR 00140/2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5700424154</t>
+          <t>5700922009</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JUARINA</t>
+          <t>GUARAI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>LD04038009</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-04 18:05</t>
+          <t>2026-01-28 20:04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7318,12 +7367,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264117059087 no ativo 5700315153 (03/02 18:07 a 04/02 21:41) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264105160221 no ativo 5700923009 (28/01 19:38 a 29/01 13:05) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>TR-5700424154 Queimadopara raios queiamdo potência 10kvatensão 34,5kvacesso livreequipe 154op01 tel-63992674347</t>
+          <t>TR-5700922009 Queimadopara raios queiamado potência 10kvatensão 34,5kvacesso livreequipe 009op01 tel-63984566867</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7338,17 +7387,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00233/2026</t>
+          <t>ETO-RD-GR 00174/2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5700569227</t>
+          <t>5747088104</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RECURSOLANDIA</t>
+          <t>BOM JESUS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7358,7 +7407,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-15 13:28</t>
+          <t>2026-02-03 13:24</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7388,12 +7437,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264128670467 no ativo 0310003104 (15/02 09:04 a 16/02 11:33) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264113090887 no ativo 5728426129 (31/01 10:20 a 04/02 06:20) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TRAFO 5745261227 SAI COM RDU DO TRAFO 5700013227 E FICA  A FRENTE DO TRAFO 5700569227 QUEIMADO PARA RAIO TAMBÉM DE 15 KVA NA NA REDE 19,9 KV ACESSO BOM PARA CAMIONETE FOI FEITO TESTE AVAZIO COSTATADO QUEIMADO COM VAZAMENTO DE ÓLEO</t>
+          <t>trafo queimado 5747088104 - 15KVA - 34,5KV - Acesso caminhonete - para raio queimadofazenda conquista - cliente Jose Reis Amario da Silva tel. 9.92521087 rdr Bom Jesus do Tocantins</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7408,27 +7457,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00259/2026</t>
+          <t>ETO-RD-GR 00189/2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5710023113</t>
+          <t>5700424154</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COUTO MAGALHAES</t>
+          <t>JUARINA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>LD01010153</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-21 13:09</t>
+          <t>2026-02-04 18:05</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7458,12 +7507,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264133424374 no ativo 5700054034 (20/02 17:32 a 21/02 14:01) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264117059087 no ativo 5700315153 (03/02 18:07 a 04/02 21:41) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>trafo queimado 5710023113 - 15KVA - 34,5KV acesso caminhonete para raio queimado necessario refazer aterramento IND ASSENTAMEN P.A. UNIAO, 0 - CHA JANDAIAuc 562509263991206181 -RDR COUTO MAGALHAES</t>
+          <t>TR-5700424154 Queimadopara raios queiamdo potência 10kvatensão 34,5kvacesso livreequipe 154op01 tel-63992674347</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7478,27 +7527,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00292/2026</t>
+          <t>ETO-RD-GR 00233/2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5710447023</t>
+          <t>5700569227</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>RECURSOLANDIA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL01020023</t>
+          <t>LD01065015</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-26 19:07</t>
+          <t>2026-02-15 13:28</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7528,12 +7577,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Mesma localidade: ocorrência 20264144238723 no ativo 5700284023 (26/02 10:01) — conferir número de série do equipamento retirado</t>
+          <t>Mesmo alimentador: ocorrência 20264128670467 no ativo 0310003104 (15/02 09:04 a 16/02 11:33) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Boa noite,Favor enviar manutenção para substituir trafo queimado 5710447023</t>
+          <t>TRAFO 5745261227 SAI COM RDU DO TRAFO 5700013227 E FICA  A FRENTE DO TRAFO 5700569227 QUEIMADO PARA RAIO TAMBÉM DE 15 KVA NA NA REDE 19,9 KV ACESSO BOM PARA CAMIONETE FOI FEITO TESTE AVAZIO COSTATADO QUEIMADO COM VAZAMENTO DE ÓLEO</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7548,37 +7597,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00295/2026</t>
+          <t>ETO-RD-GR 00259/2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5710173023</t>
+          <t>5710023113</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>COLINAS DO TOCANTINS</t>
+          <t>COUTO MAGALHAES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL05020023</t>
+          <t>LD02020023</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-27 15:07</t>
+          <t>2026-02-21 13:09</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7593,13 +7642,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264133424374 no ativo 5700054034 (20/02 17:32 a 21/02 14:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Boa tarde,Favor enviar manutenção para subsitutir trafo com bucha secundaria com defeito 5710173023Obs: Necessario substituir cruzeta deterioradaEstrutura: N3</t>
+          <t>trafo queimado 5710023113 - 15KVA - 34,5KV acesso caminhonete para raio queimado necessario refazer aterramento IND ASSENTAMEN P.A. UNIAO, 0 - CHA JANDAIAuc 562509263991206181 -RDR COUTO MAGALHAES</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7614,27 +7667,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00400/2026</t>
+          <t>ETO-RD-GR 00292/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5700214066</t>
+          <t>5710447023</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TUPIRATINS</t>
+          <t>COLINAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LD03038009</t>
+          <t>AL01020023</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-04-03 10:19</t>
+          <t>2026-02-26 19:07</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7659,17 +7712,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
+          <t>hipótese do vizinho</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
+          <t>Mesma localidade: ocorrência 20264144238723 no ativo 5700284023 (26/02 10:01) — conferir número de série do equipamento retirado</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>acionar equipe de manutencao para troca do poste e transformador no RDR de [0066] TUPIRATINStrafo 5700214066poste 10-300 id.: 49935819  estrutura u3-Tequipe 034op03</t>
+          <t>Boa noite,Favor enviar manutenção para substituir trafo queimado 5710447023</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7684,37 +7737,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00598/2026</t>
+          <t>ETO-RD-GR 00295/2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5730596155</t>
+          <t>5710173023</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PALMEIRANTE</t>
+          <t>COLINAS DO TOCANTINS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LD02020023</t>
+          <t>AL05020023</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-04 17:41</t>
+          <t>2026-02-27 15:07</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>interrompido em 1 · manobrado em 1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7729,22 +7782,18 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Mesmo alimentador: ocorrência 20264477692067 no ativo 4000514155 (04/06 16:31 a 04/06 18:04) — número operativo provavelmente trocado</t>
-        </is>
-      </c>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Boa tarde,Favor enviar manutenção para substituir trafo 5730596155 o mesmo está com muito vazamento de oléo. Se possivel colocar trafo de maior potencia.</t>
+          <t>Boa tarde,Favor enviar manutenção para subsitutir trafo com bucha secundaria com defeito 5710173023Obs: Necessario substituir cruzeta deterioradaEstrutura: N3</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO AVARIADO</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -7754,37 +7803,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00632/2026</t>
+          <t>ETO-RD-GR 00400/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5700782153</t>
+          <t>5700214066</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BERNARDO SAYAO</t>
+          <t>TUPIRATINS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LD01010153</t>
+          <t>LD03038009</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-06-19 15:57</t>
+          <t>2026-04-03 10:19</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7799,17 +7848,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>hipótese do vizinho</t>
+          <t>nada — sobe para campo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264537119402 no ativo 5700249025 (19/06 08:13 a 20/06 09:51) — número operativo provavelmente trocado</t>
+          <t>Nada encontrado no alimentador, na localidade nem em código parecido</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>TRANSFORMADOR DE 10KVA NA 34,5KV, QUEIMADO, ACESSO CAMINHONETE.</t>
+          <t>acionar equipe de manutencao para troca do poste e transformador no RDR de [0066] TUPIRATINStrafo 5700214066poste 10-300 id.: 49935819  estrutura u3-Tequipe 034op03</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7824,37 +7873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00066/2026</t>
+          <t>ETO-RD-GR 00598/2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5710535094</t>
+          <t>5730596155</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PEIXE</t>
+          <t>PALMEIRANTE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LD01066094</t>
+          <t>LD02020023</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-13 20:52</t>
+          <t>2026-06-04 17:41</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>manobrado em 1</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7874,17 +7923,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264080676346 no ativo 46810578 (13/01 09:23 a 14/01 19:34) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264477692067 no ativo 4000514155 (04/06 16:31 a 04/06 18:04) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>transformador e para raio queimado</t>
+          <t>Boa tarde,Favor enviar manutenção para substituir trafo 5730596155 o mesmo está com muito vazamento de oléo. Se possivel colocar trafo de maior potencia.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO AVARIADO</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -7894,37 +7943,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00073/2026</t>
+          <t>ETO-RD-GR 00632/2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5701108076</t>
+          <t>5700782153</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CARIRI DO TOCANTINS</t>
+          <t>BERNARDO SAYAO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LD02040003</t>
+          <t>LD01010153</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-14 16:27</t>
+          <t>2026-06-19 15:57</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>não aparece em papel nenhum</t>
+          <t>aparece, mas nunca com defeito nele</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>— nenhum</t>
+          <t>manobrado em 1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7944,17 +7993,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264082974240 no ativo 5715146076 (14/01 10:38 a 15/01 21:01) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264537119402 no ativo 5700249025 (19/06 08:13 a 20/06 09:51) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>transformador e para  raio queimado</t>
+          <t>TRANSFORMADOR DE 10KVA NA 34,5KV, QUEIMADO, ACESSO CAMINHONETE.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO COM SOBRECARGA</t>
+          <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -7964,27 +8013,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00218/2026</t>
+          <t>ETO-RD-GU 00066/2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5710863003</t>
+          <t>5710535094</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GURUPI</t>
+          <t>PEIXE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LD02001037</t>
+          <t>LD01066094</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-16 19:10</t>
+          <t>2026-01-13 20:52</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8014,17 +8063,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Mesmo alimentador: ocorrência 20264129144150 no ativo 5700423041 (16/02 14:05 a 17/02 09:20) — número operativo provavelmente trocado</t>
+          <t>Mesmo alimentador: ocorrência 20264080676346 no ativo 46810578 (13/01 09:23 a 14/01 19:34) — número operativo provavelmente trocado</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>TRAFO 5710863003 QUEIMADO EM CAMPO DE 15 KVA ACESSO PARA CAMIONETE PARA RAIO QUEIMADO</t>
+          <t>transformador e para raio queimado</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -8034,37 +8083,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00377/2026</t>
+          <t>ETO-RD-GU 00073/2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5731386073</t>
+          <t>5701108076</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LAGOA DA CONFUSAO</t>
+          <t>CARIRI DO TOCANTINS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LD06047073</t>
+          <t>LD02040003</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-23 18:27</t>
+          <t>2026-01-14 16:27</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>aparece, mas nunca com defeito nele</t>
+          <t>não aparece em papel nenhum</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>interrompido em 1 · manobrado em 2</t>
+          <t>— nenhum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8079,18 +8128,22 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>nada — sobe para campo</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264082974240 no ativo 5715146076 (14/01 10:38 a 15/01 21:01) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TRAFO 5731386073 QUEIMADO EM CAMPO DE 15 KVA ACESSO APENAS DE BARCO REGIAO ALAGADAPARA RAIO QUEIMADO   .</t>
+          <t>transformador e para  raio queimado</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>SUBST. TRAFO QUEIMADO</t>
+          <t>SUBST. TRAFO COM SOBRECARGA</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -8100,75 +8153,211 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>ETO-RD-GU 00218/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5710863003</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GURUPI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LD02001037</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-02-16 19:10</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>manobrado em 1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hipótese do vizinho</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Mesmo alimentador: ocorrência 20264129144150 no ativo 5700423041 (16/02 14:05 a 17/02 09:20) — número operativo provavelmente trocado</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>TRAFO 5710863003 QUEIMADO EM CAMPO DE 15 KVA ACESSO PARA CAMIONETE PARA RAIO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00377/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5731386073</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LAGOA DA CONFUSAO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LD06047073</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-03-23 18:27</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>aparece, mas nunca com defeito nele</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>interrompido em 1 · manobrado em 2</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>— nenhuma</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>nada — sobe para campo</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>TRAFO 5731386073 QUEIMADO EM CAMPO DE 15 KVA ACESSO APENAS DE BARCO REGIAO ALAGADAPARA RAIO QUEIMADO   .</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>SUBST. TRAFO QUEIMADO</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>ETO-RD-GU 00440/2026</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>5700284148</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>SAO VALERIO</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>LD01066094</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>2026-04-07 18:19</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>não aparece em papel nenhum</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>— nenhuma</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>— nenhum</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>— nenhum</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>hipótese do vizinho</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Mesmo alimentador: ocorrência 20264265758791 no ativo 5700693148 (07/04 11:01 a 08/04 11:30) — número operativo provavelmente trocado</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>SEGUE SS DE TRAFO QUEIMADO NA RDR DE SAO VALERIO, TRAFO DE 15KVA NA REDE DE 19.9KV, TRAFO E PARARAIO QUEIMADO, ACESSO LIVRE PARA CAMINHONETE.</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>SUBST. TRAFO QUEIMADO</t>
         </is>
       </c>
-      <c r="N78" t="n">
+      <c r="N80" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N78"/>
+  <autoFilter ref="A3:N80"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -447,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 108 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
+          <t>Os 108 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-05. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>

--- a/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
+++ b/auditoria-transformadores-134/public/bases/Sem_Interrupcao_Critica.xlsx
@@ -447,7 +447,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Os 108 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-05. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
+          <t>Os 108 que a Crítica não sustenta — conferidos contra os 7 arquivos originais da base, relidos com csv.QUOTE_NONE. Gerado de fluxo-1510.json em 2026-08-04. A divisão é a mesma da tela, e cada linha traz o que a base crua diz.</t>
         </is>
       </c>
     </row>
